--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12DE9669-E6D8-4056-8FCE-D58299642CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19F8B18-6C76-4498-8A64-B84A86E1BF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="71">
   <si>
     <t>DB1_Riglet</t>
   </si>
@@ -212,9 +212,6 @@
     <t>T10</t>
   </si>
   <si>
-    <t>L.Shoulder</t>
-  </si>
-  <si>
     <t>LWRA</t>
   </si>
   <si>
@@ -224,9 +221,6 @@
     <t>L.M5</t>
   </si>
   <si>
-    <t>R.Shoulder</t>
-  </si>
-  <si>
     <t>RWRA</t>
   </si>
   <si>
@@ -246,6 +240,15 @@
   </si>
   <si>
     <t>R.M5</t>
+  </si>
+  <si>
+    <t>R.Hip.Lat</t>
+  </si>
+  <si>
+    <t>R.Toe.lat</t>
+  </si>
+  <si>
+    <t>L.Toe.Lat</t>
   </si>
 </sst>
 </file>
@@ -323,7 +326,7 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -343,13 +346,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -684,14 +687,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A552FC-1C6B-4A74-88A1-74EB32D6F2D1}">
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="15.77734375" style="10" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="10"/>
+    <col min="1" max="5" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>50</v>
       </c>
@@ -707,8 +710,9 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>51</v>
       </c>
@@ -720,8 +724,9 @@
         <v>51</v>
       </c>
       <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>52</v>
       </c>
@@ -733,8 +738,9 @@
         <v>52</v>
       </c>
       <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="11"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>53</v>
       </c>
@@ -746,8 +752,9 @@
         <v>53</v>
       </c>
       <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
@@ -759,8 +766,9 @@
         <v>54</v>
       </c>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="11"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -772,8 +780,9 @@
         <v>4</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>57</v>
       </c>
@@ -785,8 +794,9 @@
         <v>57</v>
       </c>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>56</v>
       </c>
@@ -798,8 +808,9 @@
         <v>56</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="11"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -811,8 +822,9 @@
         <v>5</v>
       </c>
       <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="11"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>55</v>
       </c>
@@ -824,17 +836,19 @@
         <v>55</v>
       </c>
       <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>65</v>
+      <c r="F10" s="11"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -847,11 +861,10 @@
       <c r="D12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E12" s="2"/>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -863,8 +876,9 @@
         <v>36</v>
       </c>
       <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="11"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -876,8 +890,9 @@
         <v>44</v>
       </c>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="11"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -889,47 +904,51 @@
         <v>34</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="11"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="11"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="11"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -945,8 +964,9 @@
       <c r="E19" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -962,8 +982,9 @@
       <c r="E20" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -979,8 +1000,9 @@
       <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -996,8 +1018,9 @@
       <c r="E22" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="10"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>14</v>
       </c>
@@ -1013,8 +1036,9 @@
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="10"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1030,8 +1054,9 @@
       <c r="E24" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="10"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -1047,8 +1072,9 @@
       <c r="E25" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="10"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1062,8 +1088,9 @@
       <c r="E26" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" s="10"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>10</v>
       </c>
@@ -1071,12 +1098,15 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
@@ -1089,11 +1119,10 @@
       <c r="D28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E28" s="2"/>
+      <c r="F28" s="10"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>41</v>
       </c>
@@ -1105,8 +1134,9 @@
         <v>41</v>
       </c>
       <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>48</v>
       </c>
@@ -1118,8 +1148,9 @@
         <v>48</v>
       </c>
       <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" s="11"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>49</v>
       </c>
@@ -1131,47 +1162,51 @@
         <v>49</v>
       </c>
       <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
@@ -1187,8 +1222,9 @@
       <c r="E35" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" s="10"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>17</v>
       </c>
@@ -1204,8 +1240,9 @@
       <c r="E36" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" s="10"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
@@ -1219,10 +1256,11 @@
         <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
@@ -1238,8 +1276,9 @@
       <c r="E38" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" s="10"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>43</v>
       </c>
@@ -1255,8 +1294,9 @@
       <c r="E39" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39" s="10"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -1264,7 +1304,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>38</v>
@@ -1272,8 +1312,9 @@
       <c r="E40" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F40" s="10"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>42</v>
       </c>
@@ -1289,8 +1330,9 @@
       <c r="E41" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41" s="10"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>18</v>
       </c>
@@ -1304,8 +1346,9 @@
       <c r="E42" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42" s="10"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>16</v>
       </c>
@@ -1313,188 +1356,191 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
+      <c r="F43" s="10"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="9"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
+      <c r="A49" s="9"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
+      <c r="A50" s="9"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
+      <c r="A51" s="9"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
+      <c r="A52" s="9"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
+      <c r="A53" s="9"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
+      <c r="A54" s="9"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
+      <c r="A55" s="9"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
+      <c r="A56" s="9"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
+      <c r="A57" s="9"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
+      <c r="A58" s="9"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
+      <c r="A59" s="9"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
+      <c r="A60" s="9"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
+      <c r="A61" s="9"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
+      <c r="A62" s="9"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
+      <c r="A63" s="9"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
+      <c r="A64" s="9"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
+      <c r="A65" s="9"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
+      <c r="A66" s="9"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
+      <c r="A67" s="9"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
+      <c r="A68" s="9"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
+      <c r="A69" s="9"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19F8B18-6C76-4498-8A64-B84A86E1BF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA050D76-F1A4-4209-905C-F6EB73563578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
@@ -324,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -349,10 +349,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -687,11 +683,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A552FC-1C6B-4A74-88A1-74EB32D6F2D1}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="11" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
@@ -710,7 +706,6 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="11"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -724,7 +719,6 @@
         <v>51</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="11"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -738,7 +732,6 @@
         <v>52</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -752,7 +745,6 @@
         <v>53</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="11"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -766,7 +758,6 @@
         <v>54</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -780,7 +771,6 @@
         <v>4</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -794,7 +784,6 @@
         <v>57</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -808,7 +797,6 @@
         <v>56</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -822,7 +810,6 @@
         <v>5</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -836,7 +823,6 @@
         <v>55</v>
       </c>
       <c r="E10" s="8"/>
-      <c r="F10" s="11"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
@@ -846,7 +832,6 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -862,7 +847,7 @@
         <v>35</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="10"/>
+      <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
@@ -876,7 +861,6 @@
         <v>36</v>
       </c>
       <c r="E13" s="2"/>
-      <c r="F13" s="11"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
@@ -890,7 +874,6 @@
         <v>44</v>
       </c>
       <c r="E14" s="2"/>
-      <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
@@ -904,7 +887,6 @@
         <v>34</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
@@ -918,7 +900,6 @@
         <v>58</v>
       </c>
       <c r="E16" s="2"/>
-      <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -932,7 +913,6 @@
         <v>59</v>
       </c>
       <c r="E17" s="2"/>
-      <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -946,7 +926,6 @@
         <v>64</v>
       </c>
       <c r="E18" s="2"/>
-      <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
@@ -964,7 +943,7 @@
       <c r="E19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="10"/>
+      <c r="F19" s="1"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
@@ -982,7 +961,7 @@
       <c r="E20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="1"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
@@ -1000,7 +979,6 @@
       <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="11"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -1018,7 +996,7 @@
       <c r="E22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="1"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
@@ -1036,7 +1014,7 @@
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="10"/>
+      <c r="F23" s="1"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
@@ -1054,7 +1032,7 @@
       <c r="E24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="10"/>
+      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -1072,7 +1050,7 @@
       <c r="E25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="10"/>
+      <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
@@ -1088,7 +1066,7 @@
       <c r="E26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="10"/>
+      <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
@@ -1104,7 +1082,7 @@
       <c r="E27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
@@ -1120,7 +1098,7 @@
         <v>40</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="10"/>
+      <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
@@ -1134,7 +1112,6 @@
         <v>41</v>
       </c>
       <c r="E29" s="2"/>
-      <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -1148,7 +1125,6 @@
         <v>48</v>
       </c>
       <c r="E30" s="2"/>
-      <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
@@ -1162,7 +1138,6 @@
         <v>49</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -1176,7 +1151,6 @@
         <v>61</v>
       </c>
       <c r="E32" s="2"/>
-      <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
@@ -1190,7 +1164,6 @@
         <v>62</v>
       </c>
       <c r="E33" s="2"/>
-      <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
@@ -1204,7 +1177,6 @@
         <v>65</v>
       </c>
       <c r="E34" s="2"/>
-      <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
@@ -1222,7 +1194,7 @@
       <c r="E35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="10"/>
+      <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
@@ -1240,7 +1212,7 @@
       <c r="E36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F36" s="10"/>
+      <c r="F36" s="1"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
@@ -1258,7 +1230,6 @@
       <c r="E37" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
@@ -1276,7 +1247,7 @@
       <c r="E38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F38" s="10"/>
+      <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
@@ -1294,7 +1265,7 @@
       <c r="E39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="10"/>
+      <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
@@ -1312,7 +1283,7 @@
       <c r="E40" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F40" s="10"/>
+      <c r="F40" s="1"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
@@ -1330,7 +1301,7 @@
       <c r="E41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="10"/>
+      <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
@@ -1346,7 +1317,7 @@
       <c r="E42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="10"/>
+      <c r="F42" s="1"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
@@ -1362,7 +1333,7 @@
       <c r="E43" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F43" s="10"/>
+      <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA050D76-F1A4-4209-905C-F6EB73563578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5373A87-A3CE-464A-9F83-D77E46E15898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -218,9 +218,6 @@
     <t>LWRB</t>
   </si>
   <si>
-    <t>L.M5</t>
-  </si>
-  <si>
     <t>RWRA</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>R.AnkleLat</t>
   </si>
   <si>
-    <t>R.M5</t>
-  </si>
-  <si>
     <t>R.Hip.Lat</t>
   </si>
   <si>
@@ -249,6 +243,12 @@
   </si>
   <si>
     <t>L.Toe.Lat</t>
+  </si>
+  <si>
+    <t>RM5</t>
+  </si>
+  <si>
+    <t>LM5</t>
   </si>
 </sst>
 </file>
@@ -826,7 +826,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -916,14 +916,14 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -1076,11 +1076,11 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1"/>
     </row>
@@ -1141,40 +1141,40 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E34" s="2"/>
     </row>
@@ -1228,7 +1228,7 @@
         <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1275,7 +1275,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>38</v>
@@ -1327,11 +1327,11 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F43" s="1"/>
     </row>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5373A87-A3CE-464A-9F83-D77E46E15898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7155990-DB4D-45F3-8AD0-8A8CB583BDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
@@ -233,9 +233,6 @@
     <t>RFIN</t>
   </si>
   <si>
-    <t>R.AnkleLat</t>
-  </si>
-  <si>
     <t>R.Hip.Lat</t>
   </si>
   <si>
@@ -249,6 +246,9 @@
   </si>
   <si>
     <t>LM5</t>
+  </si>
+  <si>
+    <t>RAnkleLat</t>
   </si>
 </sst>
 </file>
@@ -1076,11 +1076,11 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27" s="1"/>
     </row>
@@ -1228,7 +1228,7 @@
         <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1275,7 +1275,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>38</v>
@@ -1327,11 +1327,11 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F43" s="1"/>
     </row>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7155990-DB4D-45F3-8AD0-8A8CB583BDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F627AFC-F8A0-4F03-A5D3-00E4072F4561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="70">
   <si>
     <t>DB1_Riglet</t>
   </si>
@@ -174,9 +174,6 @@
   </si>
   <si>
     <t>LVMH</t>
-  </si>
-  <si>
-    <t>LTHAP</t>
   </si>
   <si>
     <t>RVMH</t>
@@ -692,7 +689,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -709,53 +706,53 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -774,27 +771,27 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -813,20 +810,20 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -890,40 +887,40 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2"/>
     </row>
@@ -968,7 +965,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>26</v>
@@ -1076,11 +1073,11 @@
         <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F27" s="1"/>
     </row>
@@ -1115,66 +1112,66 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E34" s="2"/>
     </row>
@@ -1228,7 +1225,7 @@
         <v>39</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -1275,7 +1272,7 @@
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>38</v>
@@ -1324,14 +1321,14 @@
         <v>16</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D43" s="2"/>
       <c r="E43" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F43" s="1"/>
     </row>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F627AFC-F8A0-4F03-A5D3-00E4072F4561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1414BA-82E2-4B29-BF24-612A0B49C3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
@@ -1251,7 +1251,7 @@
         <v>43</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>32</v>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1414BA-82E2-4B29-BF24-612A0B49C3D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD00E017-865F-9E44-A1F1-3962DC7292E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
+    <workbookView xWindow="140" yWindow="920" windowWidth="29080" windowHeight="18040" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="113">
   <si>
     <t>DB1_Riglet</t>
   </si>
@@ -246,13 +246,217 @@
   </si>
   <si>
     <t>RAnkleLat</t>
+  </si>
+  <si>
+    <t>DB5_Han</t>
+  </si>
+  <si>
+    <t>head_r_ant</t>
+  </si>
+  <si>
+    <t>head_l_ant</t>
+  </si>
+  <si>
+    <t>head_r_post</t>
+  </si>
+  <si>
+    <t>head_l_post</t>
+  </si>
+  <si>
+    <t>trunk_c7</t>
+  </si>
+  <si>
+    <r>
+      <t>trunk_t8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>trunk_t12</t>
+    </r>
+  </si>
+  <si>
+    <t>trunk_t8</t>
+  </si>
+  <si>
+    <t>trunk_manu</t>
+  </si>
+  <si>
+    <t>trunk_xyph</t>
+  </si>
+  <si>
+    <t>pelvis_sac</t>
+  </si>
+  <si>
+    <t>l_acro</t>
+  </si>
+  <si>
+    <t>l_bicep</t>
+  </si>
+  <si>
+    <t>l_elb_lat</t>
+  </si>
+  <si>
+    <r>
+      <t>l_farm_ant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>l_farm_pos</t>
+    </r>
+  </si>
+  <si>
+    <t>l_wri_lat</t>
+  </si>
+  <si>
+    <t>l_wri_med</t>
+  </si>
+  <si>
+    <t>l_hand</t>
+  </si>
+  <si>
+    <t>pelvis_l_asis</t>
+  </si>
+  <si>
+    <t>pelvis_l_psis</t>
+  </si>
+  <si>
+    <t>l_thigh_antprox / l_thigh_ant</t>
+  </si>
+  <si>
+    <t>l_knee_lat</t>
+  </si>
+  <si>
+    <t>l_shank_antdist / l_shank_antprox</t>
+  </si>
+  <si>
+    <t>l_ank_lat</t>
+  </si>
+  <si>
+    <t>l_foot_heel</t>
+  </si>
+  <si>
+    <t>l_foot_toe</t>
+  </si>
+  <si>
+    <t>l_foot_m5</t>
+  </si>
+  <si>
+    <t>r_acro</t>
+  </si>
+  <si>
+    <t>r_bicep</t>
+  </si>
+  <si>
+    <t>r_elb_lat</t>
+  </si>
+  <si>
+    <r>
+      <t>r_farm_ant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>r_farm_pos</t>
+    </r>
+  </si>
+  <si>
+    <t>r_wri_lat</t>
+  </si>
+  <si>
+    <t>r_wri_med</t>
+  </si>
+  <si>
+    <t>r_hand</t>
+  </si>
+  <si>
+    <t>pelvis_r_asis</t>
+  </si>
+  <si>
+    <t>pelvis_r_psis</t>
+  </si>
+  <si>
+    <r>
+      <t>r_thigh_ant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / thigh cluster</t>
+    </r>
+  </si>
+  <si>
+    <t>r_knee_lat</t>
+  </si>
+  <si>
+    <t>r_shank_antdist / r_shank_antprox</t>
+  </si>
+  <si>
+    <t>r_ank_lat</t>
+  </si>
+  <si>
+    <t>r_foot_heel</t>
+  </si>
+  <si>
+    <t>r_foot_toe</t>
+  </si>
+  <si>
+    <t>r_foot_m5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,6 +481,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -681,13 +891,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A552FC-1C6B-4A74-88A1-74EB32D6F2D1}">
   <dimension ref="A1:F69"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="15.77734375" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" customWidth="1"/>
+    <col min="1" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="43" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>49</v>
       </c>
@@ -703,8 +913,11 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F1" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>50</v>
       </c>
@@ -716,8 +929,11 @@
         <v>50</v>
       </c>
       <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>51</v>
       </c>
@@ -729,8 +945,11 @@
         <v>51</v>
       </c>
       <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F3" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>52</v>
       </c>
@@ -742,8 +961,11 @@
         <v>52</v>
       </c>
       <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F4" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
@@ -755,8 +977,11 @@
         <v>53</v>
       </c>
       <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F5" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -768,8 +993,11 @@
         <v>4</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F6" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -781,8 +1009,11 @@
         <v>56</v>
       </c>
       <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -794,8 +1025,11 @@
         <v>55</v>
       </c>
       <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -807,8 +1041,11 @@
         <v>5</v>
       </c>
       <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>54</v>
       </c>
@@ -820,8 +1057,11 @@
         <v>54</v>
       </c>
       <c r="E10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
@@ -829,8 +1069,11 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -844,9 +1087,11 @@
         <v>35</v>
       </c>
       <c r="E12" s="2"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F12" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -858,8 +1103,11 @@
         <v>36</v>
       </c>
       <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -871,8 +1119,11 @@
         <v>44</v>
       </c>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F14" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="33" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -884,8 +1135,11 @@
         <v>34</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F15" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -897,8 +1151,11 @@
         <v>57</v>
       </c>
       <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F16" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
@@ -910,8 +1167,11 @@
         <v>58</v>
       </c>
       <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F17" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>62</v>
       </c>
@@ -923,8 +1183,11 @@
         <v>62</v>
       </c>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F18" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -940,9 +1203,11 @@
       <c r="E19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F19" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -958,9 +1223,11 @@
       <c r="E20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F20" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -976,8 +1243,11 @@
       <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F21" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -993,9 +1263,11 @@
       <c r="E22" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="1"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F22" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
         <v>14</v>
       </c>
@@ -1011,9 +1283,11 @@
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1029,9 +1303,11 @@
       <c r="E24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F24" s="1"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F24" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -1047,9 +1323,11 @@
       <c r="E25" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="1"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F25" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1063,9 +1341,11 @@
       <c r="E26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F26" s="1"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F26" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
         <v>10</v>
       </c>
@@ -1079,9 +1359,11 @@
       <c r="E27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="1"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
@@ -1095,9 +1377,11 @@
         <v>40</v>
       </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="1"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>41</v>
       </c>
@@ -1109,8 +1393,11 @@
         <v>41</v>
       </c>
       <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F29" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>47</v>
       </c>
@@ -1122,8 +1409,11 @@
         <v>47</v>
       </c>
       <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F30" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
@@ -1135,8 +1425,11 @@
         <v>48</v>
       </c>
       <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F31" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>59</v>
       </c>
@@ -1148,8 +1441,11 @@
         <v>59</v>
       </c>
       <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F32" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>60</v>
       </c>
@@ -1161,8 +1457,11 @@
         <v>60</v>
       </c>
       <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F33" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
         <v>63</v>
       </c>
@@ -1174,8 +1473,11 @@
         <v>63</v>
       </c>
       <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F34" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
@@ -1191,9 +1493,11 @@
       <c r="E35" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F35" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
         <v>17</v>
       </c>
@@ -1209,9 +1513,11 @@
       <c r="E36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F36" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
@@ -1227,8 +1533,11 @@
       <c r="E37" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F37" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
@@ -1244,9 +1553,11 @@
       <c r="E38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F38" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
         <v>43</v>
       </c>
@@ -1262,9 +1573,11 @@
       <c r="E39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F39" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -1280,9 +1593,11 @@
       <c r="E40" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F40" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>42</v>
       </c>
@@ -1298,9 +1613,11 @@
       <c r="E41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F41" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
         <v>18</v>
       </c>
@@ -1314,9 +1631,11 @@
       <c r="E42" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F42" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
         <v>16</v>
       </c>
@@ -1330,189 +1649,217 @@
       <c r="E43" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F43" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F47" s="1"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="9"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="9"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="9"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" s="1"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="9"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F51" s="1"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F52" s="1"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F53" s="1"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="9"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F54" s="1"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="9"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F55" s="1"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="9"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="9"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="9"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="9"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="9"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="9"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="9"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="9"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="9"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="9"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="9"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="9"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" s="1"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="9"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="9"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD00E017-865F-9E44-A1F1-3962DC7292E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68059376-B7AA-4FEF-9397-1C252F28F7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="920" windowWidth="29080" windowHeight="18040" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="149">
   <si>
     <t>DB1_Riglet</t>
   </si>
@@ -266,33 +266,6 @@
     <t>trunk_c7</t>
   </si>
   <si>
-    <r>
-      <t>trunk_t8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>trunk_t12</t>
-    </r>
-  </si>
-  <si>
-    <t>trunk_t8</t>
-  </si>
-  <si>
     <t>trunk_manu</t>
   </si>
   <si>
@@ -302,39 +275,9 @@
     <t>pelvis_sac</t>
   </si>
   <si>
-    <t>l_acro</t>
-  </si>
-  <si>
     <t>l_bicep</t>
   </si>
   <si>
-    <t>l_elb_lat</t>
-  </si>
-  <si>
-    <r>
-      <t>l_farm_ant</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>l_farm_pos</t>
-    </r>
-  </si>
-  <si>
     <t>l_wri_lat</t>
   </si>
   <si>
@@ -350,15 +293,9 @@
     <t>pelvis_l_psis</t>
   </si>
   <si>
-    <t>l_thigh_antprox / l_thigh_ant</t>
-  </si>
-  <si>
     <t>l_knee_lat</t>
   </si>
   <si>
-    <t>l_shank_antdist / l_shank_antprox</t>
-  </si>
-  <si>
     <t>l_ank_lat</t>
   </si>
   <si>
@@ -371,39 +308,6 @@
     <t>l_foot_m5</t>
   </si>
   <si>
-    <t>r_acro</t>
-  </si>
-  <si>
-    <t>r_bicep</t>
-  </si>
-  <si>
-    <t>r_elb_lat</t>
-  </si>
-  <si>
-    <r>
-      <t>r_farm_ant</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>r_farm_pos</t>
-    </r>
-  </si>
-  <si>
     <t>r_wri_lat</t>
   </si>
   <si>
@@ -419,27 +323,9 @@
     <t>pelvis_r_psis</t>
   </si>
   <si>
-    <r>
-      <t>r_thigh_ant</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / thigh cluster</t>
-    </r>
-  </si>
-  <si>
     <t>r_knee_lat</t>
   </si>
   <si>
-    <t>r_shank_antdist / r_shank_antprox</t>
-  </si>
-  <si>
     <t>r_ank_lat</t>
   </si>
   <si>
@@ -450,13 +336,160 @@
   </si>
   <si>
     <t>r_foot_m5</t>
+  </si>
+  <si>
+    <t>QTMMod_head_r_ant</t>
+  </si>
+  <si>
+    <t>QTMMod_head_l_ant</t>
+  </si>
+  <si>
+    <t>QTMMod_head_r_post</t>
+  </si>
+  <si>
+    <t>QTMMod_head_l_post</t>
+  </si>
+  <si>
+    <t>QTMMod_trunk_c7</t>
+  </si>
+  <si>
+    <t>QTMMod_trunk_manu</t>
+  </si>
+  <si>
+    <t>QTMMod_trunk_xyph</t>
+  </si>
+  <si>
+    <t>QTMMod_pelvis_sac</t>
+  </si>
+  <si>
+    <t>QTMMod_l_bicep</t>
+  </si>
+  <si>
+    <t>QTMMod_l_wri_lat</t>
+  </si>
+  <si>
+    <t>QTMMod_l_wri_med</t>
+  </si>
+  <si>
+    <t>QTMMod_l_hand</t>
+  </si>
+  <si>
+    <t>QTMMod_pelvis_l_asis</t>
+  </si>
+  <si>
+    <t>QTMMod_pelvis_l_psis</t>
+  </si>
+  <si>
+    <t>QTMMod_l_knee_lat</t>
+  </si>
+  <si>
+    <t>QTMMod_l_ank_lat</t>
+  </si>
+  <si>
+    <t>QTMMod_l_foot_heel</t>
+  </si>
+  <si>
+    <t>QTMMod_l_foot_toe</t>
+  </si>
+  <si>
+    <t>QTMMod_l_foot_m5</t>
+  </si>
+  <si>
+    <t>QTMMod_r_wri_lat</t>
+  </si>
+  <si>
+    <t>QTMMod_r_wri_med</t>
+  </si>
+  <si>
+    <t>QTMMod_r_hand</t>
+  </si>
+  <si>
+    <t>QTMMod_pelvis_r_asis</t>
+  </si>
+  <si>
+    <t>QTMMod_pelvis_r_psis</t>
+  </si>
+  <si>
+    <t>QTMMod_r_knee_lat</t>
+  </si>
+  <si>
+    <t>QTMMod_r_ank_lat</t>
+  </si>
+  <si>
+    <t>QTMMod_r_foot_heel</t>
+  </si>
+  <si>
+    <t>QTMMod_r_foot_toe</t>
+  </si>
+  <si>
+    <t>QTMMod_r_foot_m5</t>
+  </si>
+  <si>
+    <t>QTMMod_l_elb_med</t>
+  </si>
+  <si>
+    <t>QTMMod_r_elb_med</t>
+  </si>
+  <si>
+    <t>l_farm_ant</t>
+  </si>
+  <si>
+    <t>QTMMod_l_farm_ant</t>
+  </si>
+  <si>
+    <t>l_thigh_antprox</t>
+  </si>
+  <si>
+    <t>QTMMod_l_thigh_antprox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l_shank_antdist </t>
+  </si>
+  <si>
+    <t xml:space="preserve">QTMMod_l_shank_antdist </t>
+  </si>
+  <si>
+    <t>QTMMod_r_sho_post</t>
+  </si>
+  <si>
+    <t>r_farm_ant</t>
+  </si>
+  <si>
+    <t>QTMMod_r_farm_ant</t>
+  </si>
+  <si>
+    <t>r_shank_postprox</t>
+  </si>
+  <si>
+    <t>QTMMod_r_shank_postprox</t>
+  </si>
+  <si>
+    <t>QTMMod_trunk_l_acro</t>
+  </si>
+  <si>
+    <t>QTMMod_trunk_r_acro</t>
+  </si>
+  <si>
+    <t>trunk_l_acro</t>
+  </si>
+  <si>
+    <t>l_elb_med</t>
+  </si>
+  <si>
+    <t>trunk_r_acro</t>
+  </si>
+  <si>
+    <t>r_sho_post</t>
+  </si>
+  <si>
+    <t>r_elb_med</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,12 +514,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -531,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -554,6 +581,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -890,14 +920,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A552FC-1C6B-4A74-88A1-74EB32D6F2D1}">
-  <dimension ref="A1:F69"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G69"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5" customWidth="1"/>
+    <col min="1" max="5" width="15.77734375" customWidth="1"/>
+    <col min="6" max="7" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>49</v>
       </c>
@@ -916,8 +946,11 @@
       <c r="F1" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G1" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>50</v>
       </c>
@@ -930,10 +963,13 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>51</v>
       </c>
@@ -946,10 +982,13 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>52</v>
       </c>
@@ -962,10 +1001,13 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
@@ -978,10 +1020,13 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -994,10 +1039,13 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -1009,11 +1057,10 @@
         <v>56</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1025,11 +1072,10 @@
         <v>55</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1042,10 +1088,13 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>54</v>
       </c>
@@ -1058,10 +1107,13 @@
       </c>
       <c r="E10" s="8"/>
       <c r="F10" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>106</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
@@ -1070,10 +1122,13 @@
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -1088,10 +1143,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -1104,10 +1162,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -1120,10 +1181,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -1135,11 +1199,14 @@
         <v>34</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F15" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -1152,10 +1219,13 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
@@ -1168,10 +1238,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>62</v>
       </c>
@@ -1184,10 +1257,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
@@ -1204,10 +1280,13 @@
         <v>7</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>11</v>
       </c>
@@ -1224,10 +1303,13 @@
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>12</v>
       </c>
@@ -1243,11 +1325,14 @@
       <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F21" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>9</v>
       </c>
@@ -1264,10 +1349,13 @@
         <v>9</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>14</v>
       </c>
@@ -1283,11 +1371,14 @@
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="F23" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1304,10 +1395,13 @@
         <v>6</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>8</v>
       </c>
@@ -1324,10 +1418,13 @@
         <v>8</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>13</v>
       </c>
@@ -1342,10 +1439,13 @@
         <v>13</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>10</v>
       </c>
@@ -1360,10 +1460,13 @@
         <v>66</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
@@ -1378,10 +1481,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+        <v>143</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>41</v>
       </c>
@@ -1394,10 +1500,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>47</v>
       </c>
@@ -1410,10 +1519,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="33" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>48</v>
       </c>
@@ -1425,11 +1537,14 @@
         <v>48</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F31" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>59</v>
       </c>
@@ -1442,10 +1557,13 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>60</v>
       </c>
@@ -1458,10 +1576,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>63</v>
       </c>
@@ -1474,10 +1595,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+        <v>121</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>15</v>
       </c>
@@ -1494,10 +1618,13 @@
         <v>15</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>17</v>
       </c>
@@ -1514,10 +1641,13 @@
         <v>17</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>39</v>
       </c>
@@ -1533,11 +1663,10 @@
       <c r="E37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
@@ -1554,10 +1683,13 @@
         <v>37</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="29" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>43</v>
       </c>
@@ -1573,11 +1705,14 @@
       <c r="E39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F39" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -1594,10 +1729,13 @@
         <v>38</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>42</v>
       </c>
@@ -1614,10 +1752,13 @@
         <v>42</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>18</v>
       </c>
@@ -1632,10 +1773,13 @@
         <v>18</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>16</v>
       </c>
@@ -1650,216 +1794,245 @@
         <v>65</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="9"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G44" s="1"/>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="9"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G45" s="1"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="9"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G46" s="1"/>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="9"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="9"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G48" s="1"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="9"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G49" s="1"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="9"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="9"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G51" s="1"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="9"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="9"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G53" s="1"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="9"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G54" s="1"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="9"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G55" s="1"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="9"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G56" s="1"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="9"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="9"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G58" s="1"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="9"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G59" s="1"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="9"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G60" s="1"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="9"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G61" s="1"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="9"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G62" s="1"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="9"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G63" s="1"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="9"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="9"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G65" s="1"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="9"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G66" s="1"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="9"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G67" s="1"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="9"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G68" s="1"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="9"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68059376-B7AA-4FEF-9397-1C252F28F7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA842B-C071-43A0-ABAF-32C7CB2B7E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
@@ -531,7 +531,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -552,6 +552,17 @@
       <bottom style="thin">
         <color theme="0" tint="-0.499984740745262"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -583,7 +594,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -920,14 +931,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A552FC-1C6B-4A74-88A1-74EB32D6F2D1}">
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="5" width="15.77734375" customWidth="1"/>
-    <col min="6" max="7" width="27.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>49</v>
       </c>
@@ -950,7 +962,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>50</v>
       </c>
@@ -968,8 +980,9 @@
       <c r="G2" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>51</v>
       </c>
@@ -988,7 +1001,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>52</v>
       </c>
@@ -1007,7 +1020,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>53</v>
       </c>
@@ -1026,7 +1039,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1045,7 +1058,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>56</v>
       </c>
@@ -1057,10 +1070,10 @@
         <v>56</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1075,7 +1088,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1094,7 +1107,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>54</v>
       </c>
@@ -1113,7 +1126,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>61</v>
       </c>
@@ -1128,7 +1141,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -1149,7 +1162,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -1168,7 +1181,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -1187,7 +1200,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -1199,14 +1212,14 @@
         <v>34</v>
       </c>
       <c r="E15" s="2"/>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="2" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
@@ -1325,10 +1338,10 @@
       <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="2" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1371,10 +1384,10 @@
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="2" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1537,10 +1550,10 @@
         <v>48</v>
       </c>
       <c r="E31" s="2"/>
-      <c r="F31" s="10" t="s">
+      <c r="F31" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G31" s="10" t="s">
+      <c r="G31" s="2" t="s">
         <v>138</v>
       </c>
     </row>
@@ -1663,8 +1676,8 @@
       <c r="E37" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
@@ -1705,10 +1718,10 @@
       <c r="E39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="F39" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="G39" s="10" t="s">
+      <c r="G39" s="2" t="s">
         <v>140</v>
       </c>
     </row>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FA842B-C071-43A0-ABAF-32C7CB2B7E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B60965C6-33FD-4015-9484-4B23371684D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E84D9C67-06AA-45E9-9F3A-D00EAF183968}"/>
   </bookViews>
@@ -594,7 +594,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="199">
   <si>
     <t xml:space="preserve">Rajagopal2015_ViconPlugInGait.osim</t>
   </si>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">head_r_ant</t>
   </si>
   <si>
+    <t xml:space="preserve">R.HF</t>
+  </si>
+  <si>
     <t xml:space="preserve">LFHD</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t xml:space="preserve">head_l_ant</t>
   </si>
   <si>
+    <t xml:space="preserve"> L.HF</t>
+  </si>
+  <si>
     <t xml:space="preserve">RBHD</t>
   </si>
   <si>
@@ -238,6 +244,9 @@
     <t xml:space="preserve">pelvis_l_asis</t>
   </si>
   <si>
+    <t xml:space="preserve">L.ASIS</t>
+  </si>
+  <si>
     <t xml:space="preserve">LPSI</t>
   </si>
   <si>
@@ -253,6 +262,9 @@
     <t xml:space="preserve">pelvis_l_psis</t>
   </si>
   <si>
+    <t xml:space="preserve"> L.PSIS</t>
+  </si>
+  <si>
     <t xml:space="preserve">LTHI</t>
   </si>
   <si>
@@ -283,6 +295,9 @@
     <t xml:space="preserve">l_knee_lat</t>
   </si>
   <si>
+    <t xml:space="preserve">L.Knee</t>
+  </si>
+  <si>
     <t xml:space="preserve">LTIB</t>
   </si>
   <si>
@@ -313,6 +328,9 @@
     <t xml:space="preserve">l_ank_lat</t>
   </si>
   <si>
+    <t xml:space="preserve">L.Ankle</t>
+  </si>
+  <si>
     <t xml:space="preserve">LHEE</t>
   </si>
   <si>
@@ -328,6 +346,9 @@
     <t xml:space="preserve">l_foot_heel</t>
   </si>
   <si>
+    <t xml:space="preserve">L.Heel.Bottom</t>
+  </si>
+  <si>
     <t xml:space="preserve">LTOE</t>
   </si>
   <si>
@@ -358,6 +379,9 @@
     <t xml:space="preserve">L.Toe.Lat</t>
   </si>
   <si>
+    <t xml:space="preserve">L.MT5</t>
+  </si>
+  <si>
     <t xml:space="preserve">RSHO</t>
   </si>
   <si>
@@ -460,6 +484,9 @@
     <t xml:space="preserve">pelvis_r_asis</t>
   </si>
   <si>
+    <t xml:space="preserve">R.ASIS</t>
+  </si>
+  <si>
     <t xml:space="preserve">RPSI</t>
   </si>
   <si>
@@ -475,6 +502,9 @@
     <t xml:space="preserve">pelvis_r_psis</t>
   </si>
   <si>
+    <t xml:space="preserve"> R.PSIS</t>
+  </si>
+  <si>
     <t xml:space="preserve">RTHI</t>
   </si>
   <si>
@@ -502,6 +532,9 @@
     <t xml:space="preserve">r_knee_lat</t>
   </si>
   <si>
+    <t xml:space="preserve">R.Knee</t>
+  </si>
+  <si>
     <t xml:space="preserve">RTIB</t>
   </si>
   <si>
@@ -532,6 +565,9 @@
     <t xml:space="preserve">r_ank_lat</t>
   </si>
   <si>
+    <t xml:space="preserve">R.Ankle</t>
+  </si>
+  <si>
     <t xml:space="preserve">RHEE</t>
   </si>
   <si>
@@ -547,6 +583,9 @@
     <t xml:space="preserve">r_foot_heel</t>
   </si>
   <si>
+    <t xml:space="preserve">R.Heel.Bottom</t>
+  </si>
+  <si>
     <t xml:space="preserve">RTOE</t>
   </si>
   <si>
@@ -575,6 +614,9 @@
   </si>
   <si>
     <t xml:space="preserve">R.Toe.lat</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> R.MT5</t>
   </si>
 </sst>
 </file>
@@ -584,7 +626,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -621,6 +663,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -693,48 +740,60 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -930,1364 +989,1406 @@
   <dimension ref="A1:K1043"/>
   <sheetFormatPr defaultColWidth="8.78125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="15.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="27.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="15.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="19.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="15.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="15.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="15.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="15.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
+      <c r="I2" s="2"/>
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="K2" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1" t="s">
-        <v>14</v>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>17</v>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>20</v>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="s">
-        <v>24</v>
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="s">
-        <v>26</v>
+      <c r="A8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1" t="s">
-        <v>27</v>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="1" t="s">
-        <v>31</v>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1" t="s">
-        <v>38</v>
+      <c r="D12" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="E13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>43</v>
+      <c r="C13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1" t="s">
-        <v>47</v>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="E15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>51</v>
+      <c r="C15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1" t="s">
-        <v>55</v>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1" t="s">
-        <v>59</v>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1" t="s">
-        <v>63</v>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="C19" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>67</v>
+      <c r="D19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="A20" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>72</v>
+      <c r="C20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>77</v>
+      <c r="B21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>82</v>
+      <c r="B22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>87</v>
+      <c r="A23" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>92</v>
+      <c r="A24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>97</v>
+      <c r="A25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>102</v>
+      <c r="A26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="J27" s="1"/>
+      <c r="A27" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1" t="s">
-        <v>112</v>
+      <c r="A28" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" s="1"/>
-      <c r="E29" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1" t="s">
-        <v>117</v>
+      <c r="A29" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="E29" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1" t="s">
-        <v>121</v>
+      <c r="A30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1" t="s">
-        <v>125</v>
+      <c r="A31" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1" t="s">
-        <v>129</v>
+      <c r="A32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1" t="s">
-        <v>133</v>
+      <c r="A33" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1" t="s">
-        <v>137</v>
+      <c r="A34" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>141</v>
+      <c r="A35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>146</v>
+      <c r="A36" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>151</v>
+      <c r="A37" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="I37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>155</v>
+      <c r="A38" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>160</v>
+      <c r="A39" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>165</v>
+      <c r="A40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>170</v>
+      <c r="A41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>175</v>
+      <c r="A42" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J43" s="1"/>
+      <c r="A43" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="6" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="9"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="I45" s="13"/>
+      <c r="J45" s="13"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="9"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="I46" s="13"/>
+      <c r="J46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="I47" s="13"/>
+      <c r="J47" s="13"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
+      <c r="A48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="I48" s="13"/>
+      <c r="J48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="I49" s="13"/>
+      <c r="J49" s="13"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="9"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
+      <c r="A53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="I53" s="13"/>
+      <c r="J53" s="13"/>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="9"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
+      <c r="A54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="I54" s="13"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="9"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="9"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="9"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="9"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
+      <c r="A58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="I58" s="13"/>
+      <c r="J58" s="13"/>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="9"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="9"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="9"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="9"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
+      <c r="A62" s="12"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+      <c r="I62" s="13"/>
+      <c r="J62" s="13"/>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="9"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
+      <c r="A63" s="12"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+      <c r="I63" s="13"/>
+      <c r="J63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="9"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
+      <c r="A64" s="12"/>
+      <c r="B64" s="13"/>
+      <c r="C64" s="13"/>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="9"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="9"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="13"/>
+      <c r="C66" s="13"/>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="9"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="9"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
+      <c r="A68" s="12"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="9"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D87" s="3"/>
+      <c r="D87" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D97" s="5"/>
+      <c r="D97" s="8"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D130" s="3"/>
+      <c r="D130" s="4"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D140" s="5"/>
+      <c r="D140" s="8"/>
     </row>
     <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D173" s="3"/>
+      <c r="D173" s="4"/>
     </row>
     <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D183" s="5"/>
+      <c r="D183" s="8"/>
     </row>
     <row r="216" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D216" s="3"/>
+      <c r="D216" s="4"/>
     </row>
     <row r="226" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D226" s="5"/>
+      <c r="D226" s="8"/>
     </row>
     <row r="259" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D259" s="3"/>
+      <c r="D259" s="4"/>
     </row>
     <row r="269" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D269" s="5"/>
+      <c r="D269" s="8"/>
     </row>
     <row r="302" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D302" s="3"/>
+      <c r="D302" s="4"/>
     </row>
     <row r="312" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D312" s="5"/>
+      <c r="D312" s="8"/>
     </row>
     <row r="345" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D345" s="3"/>
+      <c r="D345" s="4"/>
     </row>
     <row r="355" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D355" s="5"/>
+      <c r="D355" s="8"/>
     </row>
     <row r="388" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D388" s="3"/>
+      <c r="D388" s="4"/>
     </row>
     <row r="398" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D398" s="5"/>
+      <c r="D398" s="8"/>
     </row>
     <row r="431" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D431" s="3"/>
+      <c r="D431" s="4"/>
     </row>
     <row r="441" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D441" s="5"/>
+      <c r="D441" s="8"/>
     </row>
     <row r="474" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D474" s="3"/>
+      <c r="D474" s="4"/>
     </row>
     <row r="484" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D484" s="5"/>
+      <c r="D484" s="8"/>
     </row>
     <row r="517" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D517" s="3"/>
+      <c r="D517" s="4"/>
     </row>
     <row r="527" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D527" s="5"/>
+      <c r="D527" s="8"/>
     </row>
     <row r="560" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D560" s="3"/>
+      <c r="D560" s="4"/>
     </row>
     <row r="570" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D570" s="5"/>
+      <c r="D570" s="8"/>
     </row>
     <row r="603" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D603" s="3"/>
+      <c r="D603" s="4"/>
     </row>
     <row r="613" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D613" s="5"/>
+      <c r="D613" s="8"/>
     </row>
     <row r="646" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D646" s="3"/>
+      <c r="D646" s="4"/>
     </row>
     <row r="656" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D656" s="5"/>
+      <c r="D656" s="8"/>
     </row>
     <row r="689" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D689" s="3"/>
+      <c r="D689" s="4"/>
     </row>
     <row r="699" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D699" s="5"/>
+      <c r="D699" s="8"/>
     </row>
     <row r="732" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D732" s="3"/>
+      <c r="D732" s="4"/>
     </row>
     <row r="742" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D742" s="5"/>
+      <c r="D742" s="8"/>
     </row>
     <row r="775" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D775" s="3"/>
+      <c r="D775" s="4"/>
     </row>
     <row r="785" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D785" s="5"/>
+      <c r="D785" s="8"/>
     </row>
     <row r="818" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D818" s="3"/>
+      <c r="D818" s="4"/>
     </row>
     <row r="828" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D828" s="5"/>
+      <c r="D828" s="8"/>
     </row>
     <row r="861" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D861" s="3"/>
+      <c r="D861" s="4"/>
     </row>
     <row r="871" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D871" s="5"/>
+      <c r="D871" s="8"/>
     </row>
     <row r="904" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D904" s="3"/>
+      <c r="D904" s="4"/>
     </row>
     <row r="914" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D914" s="5"/>
+      <c r="D914" s="8"/>
     </row>
     <row r="947" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D947" s="3"/>
+      <c r="D947" s="4"/>
     </row>
     <row r="957" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D957" s="5"/>
+      <c r="D957" s="8"/>
     </row>
     <row r="990" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D990" s="3"/>
+      <c r="D990" s="4"/>
     </row>
     <row r="1000" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1000" s="5"/>
+      <c r="D1000" s="8"/>
     </row>
     <row r="1033" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1033" s="3"/>
+      <c r="D1033" s="4"/>
     </row>
     <row r="1043" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D1043" s="5"/>
+      <c r="D1043" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6DF8DA-5566-461E-815C-1A654B0BF8E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B4978D4-200F-AA4E-AD36-03ED784CB9DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29540" yWindow="-3260" windowWidth="38080" windowHeight="20780" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="229">
   <si>
     <t>Rajagopal2015_ViconPlugInGait.osim</t>
   </si>
@@ -655,6 +655,63 @@
   </si>
   <si>
     <t>V.Sacral</t>
+  </si>
+  <si>
+    <t>DB Simonlehner</t>
+  </si>
+  <si>
+    <t>LFRA</t>
+  </si>
+  <si>
+    <t>LIAS</t>
+  </si>
+  <si>
+    <t>SACR2</t>
+  </si>
+  <si>
+    <t>LT1/LT2/LT3</t>
+  </si>
+  <si>
+    <t>LS1/LS2/LS3</t>
+  </si>
+  <si>
+    <t>RFRA</t>
+  </si>
+  <si>
+    <t>RIAS</t>
+  </si>
+  <si>
+    <t>SACR3</t>
+  </si>
+  <si>
+    <t>RT1/RT2/RT3</t>
+  </si>
+  <si>
+    <t>RS1/RS2/RS3</t>
+  </si>
+  <si>
+    <t>SACR1</t>
+  </si>
+  <si>
+    <t>LKNM</t>
+  </si>
+  <si>
+    <t>RKNM</t>
+  </si>
+  <si>
+    <t>LANM</t>
+  </si>
+  <si>
+    <t>RANM</t>
+  </si>
+  <si>
+    <t>LTOET</t>
+  </si>
+  <si>
+    <t>RTOET</t>
+  </si>
+  <si>
+    <t>Extra Markers</t>
   </si>
 </sst>
 </file>
@@ -704,7 +761,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -717,8 +774,14 @@
         <bgColor rgb="FFFFFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -741,11 +804,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -770,6 +891,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -965,22 +1101,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1043"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M1043"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="1" customWidth="1"/>
+    <col min="1" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="1" customWidth="1"/>
     <col min="5" max="5" width="27.33203125" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" customWidth="1"/>
-    <col min="7" max="7" width="3.44140625" customWidth="1"/>
-    <col min="8" max="8" width="1.88671875" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="3.5" customWidth="1"/>
+    <col min="8" max="8" width="1.83203125" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.6640625" customWidth="1"/>
-    <col min="12" max="12" width="17.109375" customWidth="1"/>
+    <col min="12" max="12" width="17.1640625" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="43" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1011,8 +1148,11 @@
       <c r="L1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -1034,8 +1174,11 @@
       <c r="K2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1057,8 +1200,11 @@
       <c r="K3" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -1077,8 +1223,11 @@
       <c r="J4" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>20</v>
       </c>
@@ -1097,8 +1246,11 @@
       <c r="J5" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -1119,8 +1271,11 @@
       <c r="J6" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1137,8 +1292,11 @@
       <c r="J7" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -1153,8 +1311,11 @@
       <c r="J8" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -1175,8 +1336,11 @@
       <c r="J9" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -1197,8 +1361,11 @@
       <c r="J10" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -1218,8 +1385,11 @@
       <c r="L11" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M11" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -1242,8 +1412,11 @@
       <c r="J12" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>46</v>
       </c>
@@ -1261,8 +1434,11 @@
       <c r="J13" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>50</v>
       </c>
@@ -1283,8 +1459,11 @@
       <c r="J14" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M14" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
@@ -1302,8 +1481,11 @@
       <c r="J15" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M15" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>58</v>
       </c>
@@ -1324,8 +1506,11 @@
       <c r="J16" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M16" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>62</v>
       </c>
@@ -1346,8 +1531,11 @@
       <c r="J17" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M17" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>66</v>
       </c>
@@ -1368,8 +1556,11 @@
       <c r="J18" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M18" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>70</v>
       </c>
@@ -1400,8 +1591,11 @@
       <c r="L19" s="6" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M19" s="12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="s">
         <v>76</v>
       </c>
@@ -1429,8 +1623,11 @@
       <c r="K20" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M20" s="12" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -1458,8 +1655,11 @@
       <c r="L21" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M21" s="12" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>88</v>
       </c>
@@ -1490,8 +1690,11 @@
       <c r="L22" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M22" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>95</v>
       </c>
@@ -1519,8 +1722,11 @@
       <c r="L23" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M23" s="12" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>101</v>
       </c>
@@ -1551,8 +1757,11 @@
       <c r="L24" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M24" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>108</v>
       </c>
@@ -1583,8 +1792,11 @@
       <c r="L25" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M25" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>114</v>
       </c>
@@ -1607,8 +1819,11 @@
       <c r="J26" s="1" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M26" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>118</v>
       </c>
@@ -1634,8 +1849,9 @@
       <c r="L27" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M27" s="1"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>125</v>
       </c>
@@ -1658,8 +1874,11 @@
       <c r="J28" s="1" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M28" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>130</v>
       </c>
@@ -1677,8 +1896,11 @@
       <c r="J29" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M29" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>134</v>
       </c>
@@ -1699,8 +1921,11 @@
       <c r="J30" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M30" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>138</v>
       </c>
@@ -1718,8 +1943,11 @@
       <c r="J31" s="1" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M31" s="12" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>142</v>
       </c>
@@ -1740,8 +1968,11 @@
       <c r="J32" s="1" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M32" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>146</v>
       </c>
@@ -1762,8 +1993,11 @@
       <c r="J33" s="1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M33" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>150</v>
       </c>
@@ -1784,8 +2018,11 @@
       <c r="J34" s="1" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M34" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>154</v>
       </c>
@@ -1816,8 +2053,11 @@
       <c r="L35" s="6" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M35" s="12" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>160</v>
       </c>
@@ -1845,8 +2085,11 @@
       <c r="K36" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M36" s="12" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>166</v>
       </c>
@@ -1870,8 +2113,11 @@
       <c r="L37" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M37" s="12" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="8" t="s">
         <v>171</v>
       </c>
@@ -1902,8 +2148,11 @@
       <c r="L38" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M38" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>178</v>
       </c>
@@ -1931,8 +2180,11 @@
       <c r="L39" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M39" s="12" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>184</v>
       </c>
@@ -1963,8 +2215,11 @@
       <c r="L40" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M40" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>191</v>
       </c>
@@ -1995,8 +2250,11 @@
       <c r="L41" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M41" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>197</v>
       </c>
@@ -2019,8 +2277,11 @@
       <c r="J42" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M42" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>201</v>
       </c>
@@ -2046,8 +2307,9 @@
       <c r="L43" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M43" s="13"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="11"/>
@@ -2056,8 +2318,11 @@
       <c r="F44" s="11"/>
       <c r="I44" s="11"/>
       <c r="J44" s="11"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M44" s="14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
@@ -2065,8 +2330,11 @@
       <c r="F45" s="11"/>
       <c r="I45" s="11"/>
       <c r="J45" s="11"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M45" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
@@ -2074,8 +2342,11 @@
       <c r="F46" s="11"/>
       <c r="I46" s="11"/>
       <c r="J46" s="11"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M46" s="15" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
@@ -2083,8 +2354,11 @@
       <c r="F47" s="11"/>
       <c r="I47" s="11"/>
       <c r="J47" s="11"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M47" s="15" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
@@ -2092,8 +2366,11 @@
       <c r="F48" s="11"/>
       <c r="I48" s="11"/>
       <c r="J48" s="11"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M48" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
@@ -2101,8 +2378,11 @@
       <c r="F49" s="11"/>
       <c r="I49" s="11"/>
       <c r="J49" s="11"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M49" s="15" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -2110,8 +2390,11 @@
       <c r="F50" s="11"/>
       <c r="I50" s="11"/>
       <c r="J50" s="11"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M50" s="15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
@@ -2119,8 +2402,11 @@
       <c r="F51" s="11"/>
       <c r="I51" s="11"/>
       <c r="J51" s="11"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="M51" s="16" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
@@ -2129,7 +2415,7 @@
       <c r="I52" s="11"/>
       <c r="J52" s="11"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
@@ -2138,7 +2424,7 @@
       <c r="I53" s="11"/>
       <c r="J53" s="11"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A54" s="10"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
@@ -2148,7 +2434,7 @@
       <c r="I54" s="11"/>
       <c r="J54" s="11"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
@@ -2157,7 +2443,7 @@
       <c r="I55" s="11"/>
       <c r="J55" s="11"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A56" s="10"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
@@ -2166,7 +2452,7 @@
       <c r="I56" s="11"/>
       <c r="J56" s="11"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A57" s="10"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
@@ -2175,7 +2461,7 @@
       <c r="I57" s="11"/>
       <c r="J57" s="11"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A58" s="10"/>
       <c r="B58" s="11"/>
       <c r="C58" s="11"/>
@@ -2184,7 +2470,7 @@
       <c r="I58" s="11"/>
       <c r="J58" s="11"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A59" s="10"/>
       <c r="B59" s="11"/>
       <c r="C59" s="11"/>
@@ -2193,7 +2479,7 @@
       <c r="I59" s="11"/>
       <c r="J59" s="11"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A60" s="10"/>
       <c r="B60" s="11"/>
       <c r="C60" s="11"/>
@@ -2202,7 +2488,7 @@
       <c r="I60" s="11"/>
       <c r="J60" s="11"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A61" s="10"/>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
@@ -2211,7 +2497,7 @@
       <c r="I61" s="11"/>
       <c r="J61" s="11"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A62" s="10"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
@@ -2220,7 +2506,7 @@
       <c r="I62" s="11"/>
       <c r="J62" s="11"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A63" s="10"/>
       <c r="B63" s="11"/>
       <c r="C63" s="11"/>
@@ -2229,7 +2515,7 @@
       <c r="I63" s="11"/>
       <c r="J63" s="11"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A64" s="10"/>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
@@ -2238,7 +2524,7 @@
       <c r="I64" s="11"/>
       <c r="J64" s="11"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" s="10"/>
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
@@ -2247,7 +2533,7 @@
       <c r="I65" s="11"/>
       <c r="J65" s="11"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" s="10"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -2256,7 +2542,7 @@
       <c r="I66" s="11"/>
       <c r="J66" s="11"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" s="10"/>
       <c r="B67" s="11"/>
       <c r="C67" s="11"/>
@@ -2265,7 +2551,7 @@
       <c r="I67" s="11"/>
       <c r="J67" s="11"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" s="10"/>
       <c r="B68" s="11"/>
       <c r="C68" s="11"/>
@@ -2274,7 +2560,7 @@
       <c r="I68" s="11"/>
       <c r="J68" s="11"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" s="10"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
@@ -2283,142 +2569,142 @@
       <c r="I69" s="11"/>
       <c r="J69" s="11"/>
     </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D87" s="3"/>
     </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D97" s="5"/>
     </row>
-    <row r="130" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D130" s="3"/>
     </row>
-    <row r="140" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D140" s="5"/>
     </row>
-    <row r="173" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D173" s="3"/>
     </row>
-    <row r="183" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D183" s="5"/>
     </row>
-    <row r="216" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D216" s="3"/>
     </row>
-    <row r="226" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D226" s="5"/>
     </row>
-    <row r="259" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="259" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D259" s="3"/>
     </row>
-    <row r="269" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="269" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D269" s="5"/>
     </row>
-    <row r="302" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="302" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D302" s="3"/>
     </row>
-    <row r="312" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="312" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D312" s="5"/>
     </row>
-    <row r="345" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="345" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D345" s="3"/>
     </row>
-    <row r="355" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="355" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D355" s="5"/>
     </row>
-    <row r="388" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="388" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D388" s="3"/>
     </row>
-    <row r="398" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="398" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D398" s="5"/>
     </row>
-    <row r="431" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="431" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D431" s="3"/>
     </row>
-    <row r="441" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="441" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D441" s="5"/>
     </row>
-    <row r="474" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="474" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D474" s="3"/>
     </row>
-    <row r="484" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="484" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D484" s="5"/>
     </row>
-    <row r="517" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="517" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D517" s="3"/>
     </row>
-    <row r="527" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="527" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D527" s="5"/>
     </row>
-    <row r="560" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="560" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D560" s="3"/>
     </row>
-    <row r="570" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="570" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D570" s="5"/>
     </row>
-    <row r="603" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="603" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D603" s="3"/>
     </row>
-    <row r="613" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="613" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D613" s="5"/>
     </row>
-    <row r="646" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="646" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D646" s="3"/>
     </row>
-    <row r="656" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="656" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D656" s="5"/>
     </row>
-    <row r="689" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="689" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D689" s="3"/>
     </row>
-    <row r="699" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="699" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D699" s="5"/>
     </row>
-    <row r="732" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="732" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D732" s="3"/>
     </row>
-    <row r="742" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="742" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D742" s="5"/>
     </row>
-    <row r="775" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="775" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D775" s="3"/>
     </row>
-    <row r="785" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="785" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D785" s="5"/>
     </row>
-    <row r="818" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="818" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D818" s="3"/>
     </row>
-    <row r="828" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="828" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D828" s="5"/>
     </row>
-    <row r="861" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="861" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D861" s="3"/>
     </row>
-    <row r="871" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="871" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D871" s="5"/>
     </row>
-    <row r="904" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="904" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D904" s="3"/>
     </row>
-    <row r="914" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="914" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D914" s="5"/>
     </row>
-    <row r="947" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="947" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D947" s="3"/>
     </row>
-    <row r="957" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="957" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D957" s="5"/>
     </row>
-    <row r="990" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="990" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D990" s="3"/>
     </row>
-    <row r="1000" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="1000" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D1000" s="5"/>
     </row>
-    <row r="1033" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="1033" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D1033" s="3"/>
     </row>
-    <row r="1043" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="1043" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D1043" s="5"/>
     </row>
   </sheetData>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3761BDE-A176-4DC2-9104-60950F8CB142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E246BF3-3571-4C78-ABDA-3F3A9BF53FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13728" yWindow="0" windowWidth="9408" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="252">
   <si>
     <t>Rajagopal2015_ViconPlugInGait.osim</t>
   </si>
@@ -657,16 +657,10 @@
     <t>LFRA</t>
   </si>
   <si>
-    <t>LIAS</t>
-  </si>
-  <si>
     <t>SACR2</t>
   </si>
   <si>
     <t>RFRA</t>
-  </si>
-  <si>
-    <t>RIAS</t>
   </si>
   <si>
     <t>SACR3</t>
@@ -1239,10 +1233,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -1251,13 +1245,13 @@
         <v>7</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>3</v>
@@ -1383,7 +1377,7 @@
         <v>22</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>22</v>
@@ -1453,7 +1447,7 @@
         <v>29</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>29</v>
@@ -1534,7 +1528,7 @@
         <v>40</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>40</v>
@@ -1710,8 +1704,8 @@
       <c r="C19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="16" t="s">
-        <v>210</v>
+      <c r="D19" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="H19" t="s">
         <v>74</v>
@@ -1720,7 +1714,7 @@
         <v>74</v>
       </c>
       <c r="J19" s="19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>69</v>
@@ -1749,13 +1743,13 @@
         <v>77</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H20" t="s">
         <v>80</v>
       </c>
       <c r="J20" s="19" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>75</v>
@@ -1784,7 +1778,7 @@
         <v>83</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="I21" t="s">
         <v>86</v>
@@ -1826,7 +1820,7 @@
         <v>93</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>87</v>
@@ -1855,7 +1849,7 @@
         <v>96</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I23" t="s">
         <v>99</v>
@@ -1897,7 +1891,7 @@
         <v>106</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>100</v>
@@ -1935,7 +1929,7 @@
         <v>112</v>
       </c>
       <c r="J25" s="19" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>107</v>
@@ -1965,7 +1959,7 @@
         <v>113</v>
       </c>
       <c r="J26" s="19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>113</v>
@@ -2001,7 +1995,7 @@
         <v>122</v>
       </c>
       <c r="J27" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>120</v>
@@ -2028,7 +2022,7 @@
         <v>124</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>124</v>
@@ -2102,7 +2096,7 @@
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J31" s="19"/>
       <c r="M31" s="1" t="s">
@@ -2204,8 +2198,8 @@
       <c r="C35" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>213</v>
+      <c r="D35" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H35" t="s">
         <v>158</v>
@@ -2214,7 +2208,7 @@
         <v>158</v>
       </c>
       <c r="J35" s="19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>153</v>
@@ -2243,13 +2237,13 @@
         <v>161</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H36" t="s">
         <v>164</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>159</v>
@@ -2278,7 +2272,7 @@
         <v>167</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="I37" t="s">
         <v>169</v>
@@ -2316,7 +2310,7 @@
         <v>176</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>170</v>
@@ -2345,7 +2339,7 @@
         <v>179</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I39" t="s">
         <v>182</v>
@@ -2387,7 +2381,7 @@
         <v>189</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>183</v>
@@ -2425,7 +2419,7 @@
         <v>195</v>
       </c>
       <c r="J41" s="19" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>190</v>
@@ -2455,7 +2449,7 @@
         <v>196</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>196</v>
@@ -2491,7 +2485,7 @@
         <v>207</v>
       </c>
       <c r="J43" s="19" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>203</v>
@@ -2519,7 +2513,7 @@
       <c r="B45" s="11"/>
       <c r="C45" s="11"/>
       <c r="D45" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M45" s="11"/>
       <c r="N45" s="11"/>
@@ -2531,7 +2525,7 @@
       <c r="B46" s="11"/>
       <c r="C46" s="11"/>
       <c r="D46" s="13" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M46" s="11"/>
       <c r="N46" s="11"/>
@@ -2543,7 +2537,7 @@
       <c r="B47" s="11"/>
       <c r="C47" s="11"/>
       <c r="D47" s="13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="M47" s="11"/>
       <c r="N47" s="11"/>
@@ -2555,7 +2549,7 @@
       <c r="B48" s="11"/>
       <c r="C48" s="11"/>
       <c r="D48" s="13" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M48" s="11"/>
       <c r="N48" s="11"/>
@@ -2567,7 +2561,7 @@
       <c r="B49" s="11"/>
       <c r="C49" s="11"/>
       <c r="D49" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M49" s="11"/>
       <c r="N49" s="11"/>
@@ -2579,7 +2573,7 @@
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
       <c r="D50" s="13" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M50" s="11"/>
       <c r="N50" s="11"/>
@@ -2591,7 +2585,7 @@
       <c r="B51" s="11"/>
       <c r="C51" s="11"/>
       <c r="D51" s="13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="M51" s="11"/>
       <c r="N51" s="11"/>
@@ -2603,7 +2597,7 @@
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
       <c r="D52" s="14" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="M52" s="11"/>
       <c r="N52" s="11"/>
@@ -2615,7 +2609,7 @@
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
       <c r="D53" s="16" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="M53" s="11"/>
       <c r="N53" s="11"/>
@@ -2627,7 +2621,7 @@
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
       <c r="D54" s="16" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="L54" s="5"/>
       <c r="M54" s="11"/>
@@ -2640,7 +2634,7 @@
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
       <c r="D55" s="16" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="M55" s="11"/>
       <c r="N55" s="11"/>
@@ -2652,7 +2646,7 @@
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
       <c r="D56" s="16" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M56" s="11"/>
       <c r="N56" s="11"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E246BF3-3571-4C78-ABDA-3F3A9BF53FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4716CA56-E1A3-4F88-AC01-8862032C3E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13728" yWindow="0" windowWidth="9408" windowHeight="12336" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="285">
   <si>
     <t>Rajagopal2015_ViconPlugInGait.osim</t>
   </si>
@@ -756,9 +757,6 @@
     <t>DB3_Simonlehner</t>
   </si>
   <si>
-    <t>DB4</t>
-  </si>
-  <si>
     <t>LT1</t>
   </si>
   <si>
@@ -781,13 +779,115 @@
   </si>
   <si>
     <t>RS1</t>
+  </si>
+  <si>
+    <t>LLK</t>
+  </si>
+  <si>
+    <t>LLA</t>
+  </si>
+  <si>
+    <t>RLK</t>
+  </si>
+  <si>
+    <t>RLA</t>
+  </si>
+  <si>
+    <t>RFM5</t>
+  </si>
+  <si>
+    <t>LFM5</t>
+  </si>
+  <si>
+    <t>RFM2</t>
+  </si>
+  <si>
+    <t>LFM2</t>
+  </si>
+  <si>
+    <t>DB_Moreira</t>
+  </si>
+  <si>
+    <t>R HEAD</t>
+  </si>
+  <si>
+    <t>L HEAD</t>
+  </si>
+  <si>
+    <t>STERNUM</t>
+  </si>
+  <si>
+    <t>L ACROMION</t>
+  </si>
+  <si>
+    <t>R ACROMION</t>
+  </si>
+  <si>
+    <t>R ILIAC</t>
+  </si>
+  <si>
+    <t>L ILIAC</t>
+  </si>
+  <si>
+    <t>R KNEE LAT</t>
+  </si>
+  <si>
+    <t>L KNEE LAT</t>
+  </si>
+  <si>
+    <t>L ANKLE LAT</t>
+  </si>
+  <si>
+    <t>R ANKLE LAT</t>
+  </si>
+  <si>
+    <t>R HEEL</t>
+  </si>
+  <si>
+    <t>L HEEL</t>
+  </si>
+  <si>
+    <t>R FOOT LAT</t>
+  </si>
+  <si>
+    <t>L FOOT LAT</t>
+  </si>
+  <si>
+    <t>L ELBOW MED</t>
+  </si>
+  <si>
+    <t>R ELBOW MED</t>
+  </si>
+  <si>
+    <t>L WRIST LAT</t>
+  </si>
+  <si>
+    <t>L WIRST MED</t>
+  </si>
+  <si>
+    <t>L HAND</t>
+  </si>
+  <si>
+    <t>R HAND</t>
+  </si>
+  <si>
+    <t>SACRUM</t>
+  </si>
+  <si>
+    <t>R WIRST LAT</t>
+  </si>
+  <si>
+    <t>R WRITS MED</t>
+  </si>
+  <si>
+    <t>DB4_Horst</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -835,6 +935,12 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -856,7 +962,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -963,11 +1069,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -981,9 +1107,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1014,6 +1137,28 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1207,11 +1352,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P1043"/>
+  <dimension ref="A1:Q1043"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="15.77734375" customWidth="1"/>
     <col min="4" max="4" width="17.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" customWidth="1"/>
     <col min="9" max="9" width="13.44140625" customWidth="1"/>
     <col min="10" max="10" width="16.109375" customWidth="1"/>
@@ -1222,7 +1368,7 @@
     <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1235,8 +1381,8 @@
       <c r="D1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>243</v>
+      <c r="E1" s="22" t="s">
+        <v>284</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -1244,7 +1390,7 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="17" t="s">
         <v>221</v>
       </c>
       <c r="L1" s="3" t="s">
@@ -1262,20 +1408,26 @@
       <c r="P1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="22" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="14" t="s">
         <v>8</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>260</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="19"/>
+      <c r="J2" s="18"/>
       <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,19 +1442,22 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="14" t="s">
         <v>12</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>261</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="18"/>
       <c r="L3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1317,16 +1472,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="18"/>
       <c r="L4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1341,16 +1496,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="19"/>
+      <c r="J5" s="18"/>
       <c r="L5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1365,7 +1520,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -1373,10 +1528,13 @@
         <v>23</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="E6" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="18" t="s">
         <v>222</v>
       </c>
       <c r="L6" s="1" t="s">
@@ -1393,7 +1551,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1401,10 +1559,10 @@
         <v>27</v>
       </c>
       <c r="C7" s="1"/>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="19"/>
+      <c r="J7" s="18"/>
       <c r="L7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1415,16 +1573,16 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
         <v>28</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="19"/>
+      <c r="J8" s="18"/>
       <c r="L8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1435,18 +1593,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
         <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="1"/>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="J9" s="18" t="s">
         <v>223</v>
       </c>
       <c r="L9" s="1" t="s">
@@ -1463,18 +1621,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="1"/>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="19"/>
+      <c r="E10" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="J10" s="18"/>
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1489,19 +1650,22 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
         <v>37</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>281</v>
       </c>
       <c r="I11" t="s">
         <v>208</v>
       </c>
-      <c r="J11" s="19"/>
+      <c r="J11" s="18"/>
       <c r="L11" s="5" t="s">
         <v>37</v>
       </c>
@@ -1514,8 +1678,8 @@
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    <row r="12" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1524,10 +1688,13 @@
       <c r="C12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="19" t="s">
+      <c r="E12" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="J12" s="18" t="s">
         <v>224</v>
       </c>
       <c r="L12" s="1" t="s">
@@ -1544,18 +1711,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
         <v>45</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="1"/>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="19"/>
+      <c r="J13" s="18"/>
       <c r="M13" s="1" t="s">
         <v>47</v>
       </c>
@@ -1567,18 +1734,21 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
         <v>49</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C14" s="1"/>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="J14" s="19"/>
+      <c r="E14" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="J14" s="18"/>
       <c r="L14" s="1" t="s">
         <v>49</v>
       </c>
@@ -1593,18 +1763,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C15" s="1"/>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="J15" s="19"/>
+      <c r="J15" s="18"/>
       <c r="M15" s="1" t="s">
         <v>55</v>
       </c>
@@ -1616,18 +1786,21 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C16" s="1"/>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="J16" s="19"/>
+      <c r="E16" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="J16" s="18"/>
       <c r="L16" s="1" t="s">
         <v>57</v>
       </c>
@@ -1642,18 +1815,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
         <v>61</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C17" s="1"/>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J17" s="19"/>
+      <c r="E17" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="J17" s="18"/>
       <c r="L17" s="1" t="s">
         <v>61</v>
       </c>
@@ -1668,18 +1844,21 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C18" s="1"/>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="J18" s="19"/>
+      <c r="E18" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="J18" s="18"/>
       <c r="L18" s="1" t="s">
         <v>65</v>
       </c>
@@ -1694,8 +1873,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
         <v>69</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1707,13 +1886,16 @@
       <c r="D19" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="E19" s="23" t="s">
+        <v>266</v>
+      </c>
       <c r="H19" t="s">
         <v>74</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="J19" s="19" t="s">
+      <c r="J19" s="18" t="s">
         <v>225</v>
       </c>
       <c r="L19" s="1" t="s">
@@ -1731,9 +1913,12 @@
       <c r="P19" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="Q19" s="23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1742,13 +1927,13 @@
       <c r="C20" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>210</v>
       </c>
       <c r="H20" t="s">
         <v>80</v>
       </c>
-      <c r="J20" s="19" t="s">
+      <c r="J20" s="18" t="s">
         <v>226</v>
       </c>
       <c r="L20" s="1" t="s">
@@ -1766,9 +1951,12 @@
       <c r="P20" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="Q20" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
         <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1777,13 +1965,13 @@
       <c r="C21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="16" t="s">
-        <v>244</v>
+      <c r="D21" s="15" t="s">
+        <v>243</v>
       </c>
       <c r="I21" t="s">
         <v>86</v>
       </c>
-      <c r="J21" s="19"/>
+      <c r="J21" s="18"/>
       <c r="L21" s="1" t="s">
         <v>81</v>
       </c>
@@ -1800,8 +1988,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+    <row r="22" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A22" s="19" t="s">
         <v>87</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1810,8 +1998,11 @@
       <c r="C22" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="14" t="s">
         <v>87</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>268</v>
       </c>
       <c r="H22" t="s">
         <v>92</v>
@@ -1819,7 +2010,7 @@
       <c r="I22" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="19" t="s">
+      <c r="J22" s="18" t="s">
         <v>227</v>
       </c>
       <c r="L22" s="1" t="s">
@@ -1837,9 +2028,12 @@
       <c r="P22" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+      <c r="Q22" s="23" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
         <v>94</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1848,13 +2042,13 @@
       <c r="C23" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="16" t="s">
-        <v>247</v>
+      <c r="D23" s="15" t="s">
+        <v>246</v>
       </c>
       <c r="I23" t="s">
         <v>99</v>
       </c>
-      <c r="J23" s="19"/>
+      <c r="J23" s="18"/>
       <c r="L23" s="1" t="s">
         <v>94</v>
       </c>
@@ -1871,8 +2065,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A24" s="19" t="s">
         <v>100</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1881,8 +2075,11 @@
       <c r="C24" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>100</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>269</v>
       </c>
       <c r="H24" t="s">
         <v>105</v>
@@ -1890,7 +2087,7 @@
       <c r="I24" t="s">
         <v>106</v>
       </c>
-      <c r="J24" s="19" t="s">
+      <c r="J24" s="18" t="s">
         <v>228</v>
       </c>
       <c r="L24" s="1" t="s">
@@ -1902,15 +2099,18 @@
       <c r="N24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O24" s="9" t="s">
+      <c r="O24" s="8" t="s">
         <v>100</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="Q24" s="24" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A25" s="19" t="s">
         <v>107</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1919,8 +2119,11 @@
       <c r="C25" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>107</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>272</v>
       </c>
       <c r="H25" t="s">
         <v>112</v>
@@ -1928,7 +2131,7 @@
       <c r="I25" t="s">
         <v>112</v>
       </c>
-      <c r="J25" s="19" t="s">
+      <c r="J25" s="18" t="s">
         <v>229</v>
       </c>
       <c r="L25" s="1" t="s">
@@ -1947,18 +2150,18 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A26" s="19" t="s">
         <v>113</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>114</v>
       </c>
       <c r="C26" s="1"/>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="19" t="s">
+      <c r="J26" s="18" t="s">
         <v>230</v>
       </c>
       <c r="L26" s="1" t="s">
@@ -1976,9 +2179,12 @@
       <c r="P26" s="1" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="Q26" s="23" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
         <v>117</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1987,14 +2193,17 @@
       <c r="C27" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="15"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="10" t="s">
+        <v>274</v>
+      </c>
       <c r="H27" t="s">
         <v>123</v>
       </c>
       <c r="I27" t="s">
         <v>122</v>
       </c>
-      <c r="J27" s="19" t="s">
+      <c r="J27" s="18" t="s">
         <v>231</v>
       </c>
       <c r="M27" s="1" t="s">
@@ -2007,9 +2216,12 @@
         <v>122</v>
       </c>
       <c r="P27" s="1"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
+      <c r="Q27" s="23" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
         <v>124</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -2018,10 +2230,13 @@
       <c r="C28" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="J28" s="19" t="s">
+      <c r="E28" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="J28" s="18" t="s">
         <v>232</v>
       </c>
       <c r="L28" s="1" t="s">
@@ -2038,18 +2253,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A29" s="19" t="s">
         <v>129</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>130</v>
       </c>
       <c r="C29" s="1"/>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="J29" s="19"/>
+      <c r="J29" s="18"/>
       <c r="M29" s="1" t="s">
         <v>131</v>
       </c>
@@ -2061,18 +2276,21 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+    <row r="30" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="A30" s="19" t="s">
         <v>133</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>134</v>
       </c>
       <c r="C30" s="1"/>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="J30" s="19"/>
+      <c r="E30" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="J30" s="18"/>
       <c r="L30" s="1" t="s">
         <v>133</v>
       </c>
@@ -2087,18 +2305,18 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A31" s="19" t="s">
         <v>137</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>138</v>
       </c>
       <c r="C31" s="1"/>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="J31" s="19"/>
+      <c r="J31" s="18"/>
       <c r="M31" s="1" t="s">
         <v>139</v>
       </c>
@@ -2110,18 +2328,21 @@
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A32" s="19" t="s">
         <v>141</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>142</v>
       </c>
       <c r="C32" s="1"/>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="J32" s="19"/>
+      <c r="E32" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="J32" s="18"/>
       <c r="L32" s="1" t="s">
         <v>141</v>
       </c>
@@ -2136,18 +2357,21 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
         <v>145</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C33" s="1"/>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="J33" s="19"/>
+      <c r="E33" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="J33" s="18"/>
       <c r="L33" s="1" t="s">
         <v>145</v>
       </c>
@@ -2162,18 +2386,21 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
         <v>149</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>150</v>
       </c>
       <c r="C34" s="1"/>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="J34" s="19"/>
+      <c r="E34" s="26" t="s">
+        <v>280</v>
+      </c>
+      <c r="J34" s="18"/>
       <c r="L34" s="1" t="s">
         <v>149</v>
       </c>
@@ -2188,7 +2415,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>153</v>
       </c>
@@ -2201,13 +2428,16 @@
       <c r="D35" s="1" t="s">
         <v>153</v>
       </c>
+      <c r="E35" s="23" t="s">
+        <v>265</v>
+      </c>
       <c r="H35" t="s">
         <v>158</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="J35" s="19" t="s">
+      <c r="J35" s="18" t="s">
         <v>233</v>
       </c>
       <c r="L35" s="1" t="s">
@@ -2225,9 +2455,12 @@
       <c r="P35" s="1" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
+      <c r="Q35" s="23" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
         <v>159</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2236,13 +2469,13 @@
       <c r="C36" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="15" t="s">
         <v>212</v>
       </c>
       <c r="H36" t="s">
         <v>164</v>
       </c>
-      <c r="J36" s="19" t="s">
+      <c r="J36" s="18" t="s">
         <v>234</v>
       </c>
       <c r="L36" s="1" t="s">
@@ -2260,9 +2493,12 @@
       <c r="P36" s="1" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="Q36" s="23" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
         <v>165</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -2271,13 +2507,13 @@
       <c r="C37" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D37" s="16" t="s">
-        <v>250</v>
+      <c r="D37" s="15" t="s">
+        <v>249</v>
       </c>
       <c r="I37" t="s">
         <v>169</v>
       </c>
-      <c r="J37" s="19"/>
+      <c r="J37" s="18"/>
       <c r="L37" s="1" t="s">
         <v>165</v>
       </c>
@@ -2290,8 +2526,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="8" t="s">
+    <row r="38" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
         <v>170</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -2300,8 +2536,11 @@
       <c r="C38" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="14" t="s">
         <v>170</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>267</v>
       </c>
       <c r="H38" t="s">
         <v>175</v>
@@ -2309,7 +2548,7 @@
       <c r="I38" t="s">
         <v>176</v>
       </c>
-      <c r="J38" s="19" t="s">
+      <c r="J38" s="18" t="s">
         <v>235</v>
       </c>
       <c r="L38" s="1" t="s">
@@ -2327,9 +2566,12 @@
       <c r="P38" s="1" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
+      <c r="Q38" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -2338,13 +2580,13 @@
       <c r="C39" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D39" s="16" t="s">
-        <v>251</v>
+      <c r="D39" s="15" t="s">
+        <v>250</v>
       </c>
       <c r="I39" t="s">
         <v>182</v>
       </c>
-      <c r="J39" s="19"/>
+      <c r="J39" s="18"/>
       <c r="L39" s="1" t="s">
         <v>177</v>
       </c>
@@ -2361,7 +2603,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" ht="27" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>183</v>
       </c>
@@ -2371,8 +2613,11 @@
       <c r="C40" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="14" t="s">
         <v>183</v>
+      </c>
+      <c r="E40" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="H40" t="s">
         <v>188</v>
@@ -2380,7 +2625,7 @@
       <c r="I40" t="s">
         <v>189</v>
       </c>
-      <c r="J40" s="19" t="s">
+      <c r="J40" s="18" t="s">
         <v>236</v>
       </c>
       <c r="L40" s="1" t="s">
@@ -2398,8 +2643,11 @@
       <c r="P40" s="1" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q40" s="24" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>190</v>
       </c>
@@ -2409,8 +2657,11 @@
       <c r="C41" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="14" t="s">
         <v>190</v>
+      </c>
+      <c r="E41" s="24" t="s">
+        <v>271</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -2418,7 +2669,7 @@
       <c r="I41" t="s">
         <v>195</v>
       </c>
-      <c r="J41" s="19" t="s">
+      <c r="J41" s="18" t="s">
         <v>237</v>
       </c>
       <c r="L41" s="1" t="s">
@@ -2437,18 +2688,18 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A42" s="8" t="s">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
         <v>196</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>197</v>
       </c>
       <c r="C42" s="1"/>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="J42" s="19" t="s">
+      <c r="J42" s="18" t="s">
         <v>238</v>
       </c>
       <c r="L42" s="1" t="s">
@@ -2466,9 +2717,12 @@
       <c r="P42" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A43" s="8" t="s">
+      <c r="Q42" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
         <v>200</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -2477,14 +2731,17 @@
       <c r="C43" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="17"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="10" t="s">
+        <v>273</v>
+      </c>
       <c r="H43" t="s">
         <v>206</v>
       </c>
       <c r="I43" t="s">
         <v>207</v>
       </c>
-      <c r="J43" s="19" t="s">
+      <c r="J43" s="18" t="s">
         <v>239</v>
       </c>
       <c r="M43" s="1" t="s">
@@ -2497,278 +2754,281 @@
         <v>205</v>
       </c>
       <c r="P43" s="1"/>
-    </row>
-    <row r="44" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
+      <c r="Q43" s="23" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="9"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
       <c r="L44" s="3"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="12" t="s">
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="13" t="s">
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A46" s="9"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="12" t="s">
         <v>213</v>
       </c>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="13" t="s">
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="13" t="s">
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A48" s="9"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="M48" s="11"/>
-      <c r="N48" s="11"/>
-      <c r="O48" s="11"/>
-      <c r="P48" s="11"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="13" t="s">
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="M49" s="11"/>
-      <c r="N49" s="11"/>
-      <c r="O49" s="11"/>
-      <c r="P49" s="11"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="13" t="s">
+      <c r="A50" s="9"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="13" t="s">
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
     </row>
     <row r="52" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="14" t="s">
+      <c r="A52" s="9"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="16" t="s">
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A54" s="9"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="11"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="10"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="16" t="s">
-        <v>246</v>
-      </c>
       <c r="L54" s="5"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="11"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A55" s="10"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="16" t="s">
+      <c r="A55" s="9"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A56" s="9"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="M55" s="11"/>
-      <c r="N55" s="11"/>
-      <c r="O55" s="11"/>
-      <c r="P55" s="11"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" s="10"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="10"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="11"/>
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="10"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="M58" s="11"/>
-      <c r="N58" s="11"/>
-      <c r="O58" s="11"/>
-      <c r="P58" s="11"/>
+      <c r="A58" s="9"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="10"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="M59" s="11"/>
-      <c r="N59" s="11"/>
-      <c r="O59" s="11"/>
-      <c r="P59" s="11"/>
+      <c r="A59" s="9"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="10"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="M60" s="11"/>
-      <c r="N60" s="11"/>
-      <c r="O60" s="11"/>
-      <c r="P60" s="11"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="10"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="M61" s="11"/>
-      <c r="N61" s="11"/>
-      <c r="O61" s="11"/>
-      <c r="P61" s="11"/>
+      <c r="A61" s="9"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="10"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="M62" s="11"/>
-      <c r="N62" s="11"/>
-      <c r="O62" s="11"/>
-      <c r="P62" s="11"/>
+      <c r="A62" s="9"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="10"/>
+      <c r="P62" s="10"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="10"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="11"/>
-      <c r="O63" s="11"/>
-      <c r="P63" s="11"/>
+      <c r="A63" s="9"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="10"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" s="10"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="M64" s="11"/>
-      <c r="N64" s="11"/>
-      <c r="O64" s="11"/>
-      <c r="P64" s="11"/>
+      <c r="A64" s="9"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="10"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="10"/>
+      <c r="P64" s="10"/>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="10"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="11"/>
-      <c r="O65" s="11"/>
-      <c r="P65" s="11"/>
+      <c r="A65" s="9"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="10"/>
+      <c r="P65" s="10"/>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="10"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="M66" s="11"/>
-      <c r="N66" s="11"/>
-      <c r="O66" s="11"/>
-      <c r="P66" s="11"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="10"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="10"/>
+      <c r="P66" s="10"/>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A67" s="10"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="11"/>
-      <c r="O67" s="11"/>
-      <c r="P67" s="11"/>
+      <c r="A67" s="9"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="10"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" s="10"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="M68" s="11"/>
-      <c r="N68" s="11"/>
-      <c r="O68" s="11"/>
-      <c r="P68" s="11"/>
+      <c r="A68" s="9"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="10"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="10"/>
+      <c r="P68" s="10"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" s="10"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="11"/>
-      <c r="P69" s="11"/>
+      <c r="A69" s="9"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="10"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="10"/>
+      <c r="P69" s="10"/>
     </row>
     <row r="87" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L87" s="3"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4716CA56-E1A3-4F88-AC01-8862032C3E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D7995C-1489-45CA-94A7-793C9C36438F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -1093,7 +1092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1151,12 +1150,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1358,9 +1351,9 @@
     <col min="1" max="3" width="15.77734375" customWidth="1"/>
     <col min="4" max="4" width="17.5546875" customWidth="1"/>
     <col min="5" max="5" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" customWidth="1"/>
     <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="10" max="10" width="16.109375" customWidth="1"/>
     <col min="12" max="12" width="15.77734375" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.33203125" customWidth="1"/>
     <col min="14" max="14" width="15.44140625" customWidth="1"/>
@@ -1384,14 +1377,14 @@
       <c r="E1" s="22" t="s">
         <v>284</v>
       </c>
+      <c r="F1" s="17" t="s">
+        <v>221</v>
+      </c>
       <c r="H1" t="s">
         <v>6</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>221</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>240</v>
@@ -1424,10 +1417,10 @@
       <c r="E2" s="24" t="s">
         <v>260</v>
       </c>
+      <c r="F2" s="18"/>
       <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="18"/>
       <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1454,10 +1447,10 @@
       <c r="E3" s="24" t="s">
         <v>261</v>
       </c>
+      <c r="F3" s="18"/>
       <c r="H3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="18"/>
       <c r="L3" s="1" t="s">
         <v>12</v>
       </c>
@@ -1481,7 +1474,7 @@
       <c r="D4" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="L4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1505,7 +1498,7 @@
       <c r="D5" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="18"/>
+      <c r="F5" s="18"/>
       <c r="L5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1534,7 +1527,7 @@
       <c r="E6" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="F6" s="18" t="s">
         <v>222</v>
       </c>
       <c r="L6" s="1" t="s">
@@ -1562,7 +1555,7 @@
       <c r="D7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="18"/>
+      <c r="F7" s="18"/>
       <c r="L7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1582,7 +1575,7 @@
       <c r="D8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="J8" s="18"/>
+      <c r="F8" s="18"/>
       <c r="L8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1604,7 +1597,7 @@
       <c r="D9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="F9" s="18" t="s">
         <v>223</v>
       </c>
       <c r="L9" s="1" t="s">
@@ -1621,7 +1614,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>33</v>
       </c>
@@ -1635,7 +1628,7 @@
       <c r="E10" s="24" t="s">
         <v>262</v>
       </c>
-      <c r="J10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1662,10 +1655,10 @@
       <c r="E11" t="s">
         <v>281</v>
       </c>
+      <c r="F11" s="18"/>
       <c r="I11" t="s">
         <v>208</v>
       </c>
-      <c r="J11" s="18"/>
       <c r="L11" s="5" t="s">
         <v>37</v>
       </c>
@@ -1678,7 +1671,7 @@
       <c r="O11" s="5"/>
       <c r="P11" s="5"/>
     </row>
-    <row r="12" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
         <v>40</v>
       </c>
@@ -1694,7 +1687,7 @@
       <c r="E12" s="24" t="s">
         <v>263</v>
       </c>
-      <c r="J12" s="18" t="s">
+      <c r="F12" s="18" t="s">
         <v>224</v>
       </c>
       <c r="L12" s="1" t="s">
@@ -1722,7 +1715,7 @@
       <c r="D13" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="J13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="M13" s="1" t="s">
         <v>47</v>
       </c>
@@ -1734,7 +1727,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
         <v>49</v>
       </c>
@@ -1745,10 +1738,10 @@
       <c r="D14" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="J14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="L14" s="1" t="s">
         <v>49</v>
       </c>
@@ -1774,7 +1767,7 @@
       <c r="D15" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="J15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="M15" s="1" t="s">
         <v>55</v>
       </c>
@@ -1786,7 +1779,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>57</v>
       </c>
@@ -1797,10 +1790,10 @@
       <c r="D16" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="24" t="s">
         <v>277</v>
       </c>
-      <c r="J16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="L16" s="1" t="s">
         <v>57</v>
       </c>
@@ -1815,7 +1808,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="19" t="s">
         <v>61</v>
       </c>
@@ -1826,10 +1819,10 @@
       <c r="D17" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="24" t="s">
         <v>278</v>
       </c>
-      <c r="J17" s="18"/>
+      <c r="F17" s="18"/>
       <c r="L17" s="1" t="s">
         <v>61</v>
       </c>
@@ -1855,10 +1848,10 @@
       <c r="D18" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="E18" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="J18" s="18"/>
+      <c r="F18" s="18"/>
       <c r="L18" s="1" t="s">
         <v>65</v>
       </c>
@@ -1889,14 +1882,14 @@
       <c r="E19" s="23" t="s">
         <v>266</v>
       </c>
+      <c r="F19" s="18" t="s">
+        <v>225</v>
+      </c>
       <c r="H19" t="s">
         <v>74</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>225</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>69</v>
@@ -1930,11 +1923,11 @@
       <c r="D20" s="15" t="s">
         <v>210</v>
       </c>
+      <c r="F20" s="18" t="s">
+        <v>226</v>
+      </c>
       <c r="H20" t="s">
         <v>80</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>226</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>75</v>
@@ -1968,10 +1961,10 @@
       <c r="D21" s="15" t="s">
         <v>243</v>
       </c>
+      <c r="F21" s="18"/>
       <c r="I21" t="s">
         <v>86</v>
       </c>
-      <c r="J21" s="18"/>
       <c r="L21" s="1" t="s">
         <v>81</v>
       </c>
@@ -1988,7 +1981,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>87</v>
       </c>
@@ -2004,14 +1997,14 @@
       <c r="E22" s="23" t="s">
         <v>268</v>
       </c>
+      <c r="F22" s="18" t="s">
+        <v>227</v>
+      </c>
       <c r="H22" t="s">
         <v>92</v>
       </c>
       <c r="I22" t="s">
         <v>93</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>227</v>
       </c>
       <c r="L22" s="1" t="s">
         <v>87</v>
@@ -2045,10 +2038,10 @@
       <c r="D23" s="15" t="s">
         <v>246</v>
       </c>
+      <c r="F23" s="18"/>
       <c r="I23" t="s">
         <v>99</v>
       </c>
-      <c r="J23" s="18"/>
       <c r="L23" s="1" t="s">
         <v>94</v>
       </c>
@@ -2065,7 +2058,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="19" t="s">
         <v>100</v>
       </c>
@@ -2081,14 +2074,14 @@
       <c r="E24" s="24" t="s">
         <v>269</v>
       </c>
+      <c r="F24" s="18" t="s">
+        <v>228</v>
+      </c>
       <c r="H24" t="s">
         <v>105</v>
       </c>
       <c r="I24" t="s">
         <v>106</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>228</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>100</v>
@@ -2125,14 +2118,14 @@
       <c r="E25" s="24" t="s">
         <v>272</v>
       </c>
+      <c r="F25" s="18" t="s">
+        <v>229</v>
+      </c>
       <c r="H25" t="s">
         <v>112</v>
       </c>
       <c r="I25" t="s">
         <v>112</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>229</v>
       </c>
       <c r="L25" s="1" t="s">
         <v>107</v>
@@ -2161,7 +2154,7 @@
       <c r="D26" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="18" t="s">
+      <c r="F26" s="18" t="s">
         <v>230</v>
       </c>
       <c r="L26" s="1" t="s">
@@ -2183,7 +2176,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>117</v>
       </c>
@@ -2197,14 +2190,14 @@
       <c r="E27" s="10" t="s">
         <v>274</v>
       </c>
+      <c r="F27" s="18" t="s">
+        <v>231</v>
+      </c>
       <c r="H27" t="s">
         <v>123</v>
       </c>
       <c r="I27" t="s">
         <v>122</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>231</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>120</v>
@@ -2220,7 +2213,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
         <v>124</v>
       </c>
@@ -2236,7 +2229,7 @@
       <c r="E28" s="24" t="s">
         <v>264</v>
       </c>
-      <c r="J28" s="18" t="s">
+      <c r="F28" s="18" t="s">
         <v>232</v>
       </c>
       <c r="L28" s="1" t="s">
@@ -2264,7 +2257,7 @@
       <c r="D29" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="J29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="M29" s="1" t="s">
         <v>131</v>
       </c>
@@ -2276,7 +2269,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>133</v>
       </c>
@@ -2287,10 +2280,10 @@
       <c r="D30" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="E30" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="J30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="L30" s="1" t="s">
         <v>133</v>
       </c>
@@ -2316,7 +2309,7 @@
       <c r="D31" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="J31" s="18"/>
+      <c r="F31" s="18"/>
       <c r="M31" s="1" t="s">
         <v>139</v>
       </c>
@@ -2328,7 +2321,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>141</v>
       </c>
@@ -2339,10 +2332,10 @@
       <c r="D32" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="25" t="s">
+      <c r="E32" s="24" t="s">
         <v>282</v>
       </c>
-      <c r="J32" s="18"/>
+      <c r="F32" s="18"/>
       <c r="L32" s="1" t="s">
         <v>141</v>
       </c>
@@ -2357,7 +2350,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>145</v>
       </c>
@@ -2368,10 +2361,10 @@
       <c r="D33" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="E33" s="25" t="s">
+      <c r="E33" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="J33" s="18"/>
+      <c r="F33" s="18"/>
       <c r="L33" s="1" t="s">
         <v>145</v>
       </c>
@@ -2397,10 +2390,10 @@
       <c r="D34" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="26" t="s">
+      <c r="E34" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="J34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="L34" s="1" t="s">
         <v>149</v>
       </c>
@@ -2431,14 +2424,14 @@
       <c r="E35" s="23" t="s">
         <v>265</v>
       </c>
+      <c r="F35" s="18" t="s">
+        <v>233</v>
+      </c>
       <c r="H35" t="s">
         <v>158</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="J35" s="18" t="s">
-        <v>233</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>153</v>
@@ -2472,11 +2465,11 @@
       <c r="D36" s="15" t="s">
         <v>212</v>
       </c>
+      <c r="F36" s="18" t="s">
+        <v>234</v>
+      </c>
       <c r="H36" t="s">
         <v>164</v>
-      </c>
-      <c r="J36" s="18" t="s">
-        <v>234</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>159</v>
@@ -2510,10 +2503,10 @@
       <c r="D37" s="15" t="s">
         <v>249</v>
       </c>
+      <c r="F37" s="18"/>
       <c r="I37" t="s">
         <v>169</v>
       </c>
-      <c r="J37" s="18"/>
       <c r="L37" s="1" t="s">
         <v>165</v>
       </c>
@@ -2526,7 +2519,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>170</v>
       </c>
@@ -2542,14 +2535,14 @@
       <c r="E38" s="23" t="s">
         <v>267</v>
       </c>
+      <c r="F38" s="18" t="s">
+        <v>235</v>
+      </c>
       <c r="H38" t="s">
         <v>175</v>
       </c>
       <c r="I38" t="s">
         <v>176</v>
-      </c>
-      <c r="J38" s="18" t="s">
-        <v>235</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>170</v>
@@ -2583,10 +2576,10 @@
       <c r="D39" s="15" t="s">
         <v>250</v>
       </c>
+      <c r="F39" s="18"/>
       <c r="I39" t="s">
         <v>182</v>
       </c>
-      <c r="J39" s="18"/>
       <c r="L39" s="1" t="s">
         <v>177</v>
       </c>
@@ -2603,7 +2596,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>183</v>
       </c>
@@ -2619,14 +2612,14 @@
       <c r="E40" s="24" t="s">
         <v>270</v>
       </c>
+      <c r="F40" s="18" t="s">
+        <v>236</v>
+      </c>
       <c r="H40" t="s">
         <v>188</v>
       </c>
       <c r="I40" t="s">
         <v>189</v>
-      </c>
-      <c r="J40" s="18" t="s">
-        <v>236</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>183</v>
@@ -2663,14 +2656,14 @@
       <c r="E41" s="24" t="s">
         <v>271</v>
       </c>
+      <c r="F41" s="18" t="s">
+        <v>237</v>
+      </c>
       <c r="H41" t="s">
         <v>195</v>
       </c>
       <c r="I41" t="s">
         <v>195</v>
-      </c>
-      <c r="J41" s="18" t="s">
-        <v>237</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>190</v>
@@ -2699,7 +2692,7 @@
       <c r="D42" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="J42" s="18" t="s">
+      <c r="F42" s="18" t="s">
         <v>238</v>
       </c>
       <c r="L42" s="1" t="s">
@@ -2721,7 +2714,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="43" spans="1:17" ht="27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>200</v>
       </c>
@@ -2735,14 +2728,14 @@
       <c r="E43" s="10" t="s">
         <v>273</v>
       </c>
+      <c r="F43" s="18" t="s">
+        <v>239</v>
+      </c>
       <c r="H43" t="s">
         <v>206</v>
       </c>
       <c r="I43" t="s">
         <v>207</v>
-      </c>
-      <c r="J43" s="18" t="s">
-        <v>239</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>203</v>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D7995C-1489-45CA-94A7-793C9C36438F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF063078-A0C0-5943-995E-168BCC65C212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="840" windowWidth="12580" windowHeight="15640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -690,9 +690,6 @@
     <t>Extra Markers</t>
   </si>
   <si>
-    <t>Kuopio marker</t>
-  </si>
-  <si>
     <t>Torso4</t>
   </si>
   <si>
@@ -880,13 +877,16 @@
   </si>
   <si>
     <t>DB4_Horst</t>
+  </si>
+  <si>
+    <t>DB5_Kuopio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -929,19 +929,29 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -956,12 +966,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1061,17 +1077,6 @@
       <left style="thin">
         <color theme="0" tint="-0.499984740745262"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
       <right style="thin">
         <color theme="0" tint="-0.499984740745262"/>
       </right>
@@ -1092,13 +1097,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1106,7 +1108,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1116,42 +1117,67 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1346,78 +1372,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q1043"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="15.77734375" customWidth="1"/>
-    <col min="4" max="4" width="17.5546875" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" customWidth="1"/>
-    <col min="6" max="6" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="41.1640625" customWidth="1"/>
+    <col min="2" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="13" customWidth="1"/>
+    <col min="5" max="6" width="17.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" customWidth="1"/>
-    <col min="12" max="12" width="15.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" style="1" customWidth="1"/>
     <col min="13" max="13" width="27.33203125" customWidth="1"/>
-    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="14" max="14" width="15.5" customWidth="1"/>
     <col min="15" max="15" width="10" customWidth="1"/>
     <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="40.200000000000003" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:17" s="23" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="E1" s="22" t="s">
+      <c r="D1" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="F1" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="F1" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="H1" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="M1" s="24" t="s">
         <v>240</v>
       </c>
-      <c r="M1" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="Q1" s="25" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="F2" s="18"/>
+      <c r="F2" s="28"/>
       <c r="H2" t="s">
         <v>11</v>
       </c>
@@ -1435,20 +1461,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="14" t="s">
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="F3" s="18"/>
-      <c r="H3" s="4" t="s">
+      <c r="E3" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="F3" s="28"/>
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
       <c r="L3" s="1" t="s">
@@ -1465,16 +1491,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="14" t="s">
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="18"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
       <c r="L4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1489,16 +1516,17 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="14" t="s">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="18"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
       <c r="L5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1513,22 +1541,22 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="14" t="s">
+      <c r="C6" s="28"/>
+      <c r="D6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>222</v>
+      <c r="F6" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>22</v>
@@ -1544,18 +1572,19 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="14" t="s">
+      <c r="C7" s="28"/>
+      <c r="D7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="18"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
       <c r="L7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1566,16 +1595,17 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="14" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="18"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
       <c r="L8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1586,19 +1616,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="28"/>
+      <c r="D9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>223</v>
+      <c r="E9" s="29"/>
+      <c r="F9" s="9" t="s">
+        <v>222</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>29</v>
@@ -1614,21 +1645,21 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="14" t="s">
+      <c r="C10" s="28"/>
+      <c r="D10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="F10" s="18"/>
+      <c r="E10" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="28"/>
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1638,57 +1669,57 @@
       <c r="N10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O10" s="5"/>
+      <c r="O10" s="4"/>
       <c r="P10" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="14" t="s">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E11" t="s">
-        <v>281</v>
-      </c>
-      <c r="F11" s="18"/>
+      <c r="E11" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="F11" s="29"/>
       <c r="I11" t="s">
         <v>208</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="F12" s="18" t="s">
-        <v>224</v>
+      <c r="E12" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>223</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>40</v>
@@ -1704,18 +1735,19 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="28"/>
+      <c r="D13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="18"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
       <c r="M13" s="1" t="s">
         <v>47</v>
       </c>
@@ -1727,21 +1759,21 @@
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="F14" s="18"/>
+      <c r="E14" s="17" t="s">
+        <v>274</v>
+      </c>
+      <c r="F14" s="28"/>
       <c r="L14" s="1" t="s">
         <v>49</v>
       </c>
@@ -1756,18 +1788,19 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="15" t="s">
+      <c r="C15" s="28"/>
+      <c r="D15" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="18"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
       <c r="M15" s="1" t="s">
         <v>55</v>
       </c>
@@ -1779,21 +1812,21 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="14" t="s">
+      <c r="C16" s="28"/>
+      <c r="D16" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="F16" s="18"/>
+      <c r="E16" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" s="28"/>
       <c r="L16" s="1" t="s">
         <v>57</v>
       </c>
@@ -1808,21 +1841,21 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="14" t="s">
+      <c r="C17" s="28"/>
+      <c r="D17" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="24" t="s">
-        <v>278</v>
-      </c>
-      <c r="F17" s="18"/>
+      <c r="E17" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="F17" s="28"/>
       <c r="L17" s="1" t="s">
         <v>61</v>
       </c>
@@ -1837,21 +1870,21 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="14" t="s">
+      <c r="C18" s="28"/>
+      <c r="D18" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="F18" s="18"/>
+      <c r="E18" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="F18" s="28"/>
       <c r="L18" s="1" t="s">
         <v>65</v>
       </c>
@@ -1866,29 +1899,29 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="23" t="s">
-        <v>266</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>225</v>
+      <c r="E19" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>224</v>
       </c>
       <c r="H19" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="5" t="s">
         <v>74</v>
       </c>
       <c r="L19" s="1" t="s">
@@ -1906,25 +1939,26 @@
       <c r="P19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Q19" s="23" t="s">
+      <c r="Q19" s="10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="F20" s="18" t="s">
-        <v>226</v>
+      <c r="E20" s="29"/>
+      <c r="F20" s="9" t="s">
+        <v>225</v>
       </c>
       <c r="H20" t="s">
         <v>80</v>
@@ -1944,24 +1978,25 @@
       <c r="P20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Q20" s="23" t="s">
+      <c r="Q20" s="10" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="F21" s="18"/>
+      <c r="D21" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
       <c r="I21" t="s">
         <v>86</v>
       </c>
@@ -1981,24 +2016,24 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="23" t="s">
-        <v>268</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>227</v>
+      <c r="E22" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>226</v>
       </c>
       <c r="H22" t="s">
         <v>92</v>
@@ -2021,24 +2056,25 @@
       <c r="P22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q22" s="23" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q22" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="F23" s="18"/>
+      <c r="D23" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
       <c r="I23" t="s">
         <v>99</v>
       </c>
@@ -2058,24 +2094,24 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="19" t="s">
+    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="24" t="s">
-        <v>269</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>228</v>
+      <c r="E24" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="H24" t="s">
         <v>105</v>
@@ -2092,34 +2128,34 @@
       <c r="N24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O24" s="8" t="s">
+      <c r="O24" s="6" t="s">
         <v>100</v>
       </c>
       <c r="P24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="Q24" s="24" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="19" t="s">
+      <c r="Q24" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A25" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>229</v>
+      <c r="E25" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>228</v>
       </c>
       <c r="H25" t="s">
         <v>112</v>
@@ -2143,19 +2179,20 @@
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="14" t="s">
+      <c r="C26" s="28"/>
+      <c r="D26" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F26" s="18" t="s">
-        <v>230</v>
+      <c r="E26" s="29"/>
+      <c r="F26" s="9" t="s">
+        <v>229</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>113</v>
@@ -2172,26 +2209,26 @@
       <c r="P26" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Q26" s="23" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q26" s="10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>231</v>
+      <c r="D27" s="28"/>
+      <c r="E27" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="F27" s="17" t="s">
+        <v>230</v>
       </c>
       <c r="H27" t="s">
         <v>123</v>
@@ -2209,28 +2246,28 @@
         <v>122</v>
       </c>
       <c r="P27" s="1"/>
-      <c r="Q27" s="23" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="s">
+      <c r="Q27" s="10" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="E28" s="24" t="s">
-        <v>264</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>232</v>
+      <c r="E28" s="17" t="s">
+        <v>263</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>231</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>124</v>
@@ -2246,18 +2283,19 @@
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="14" t="s">
+      <c r="C29" s="28"/>
+      <c r="D29" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="F29" s="18"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
       <c r="M29" s="1" t="s">
         <v>131</v>
       </c>
@@ -2269,21 +2307,21 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="14" t="s">
+      <c r="C30" s="28"/>
+      <c r="D30" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="F30" s="18"/>
+      <c r="E30" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="F30" s="28"/>
       <c r="L30" s="1" t="s">
         <v>133</v>
       </c>
@@ -2298,18 +2336,19 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="28"/>
+      <c r="D31" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="F31" s="18"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
       <c r="M31" s="1" t="s">
         <v>139</v>
       </c>
@@ -2321,21 +2360,21 @@
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="14" t="s">
+      <c r="C32" s="28"/>
+      <c r="D32" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="24" t="s">
-        <v>282</v>
-      </c>
-      <c r="F32" s="18"/>
+      <c r="E32" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="F32" s="28"/>
       <c r="L32" s="1" t="s">
         <v>141</v>
       </c>
@@ -2350,21 +2389,21 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="14" t="s">
+      <c r="C33" s="28"/>
+      <c r="D33" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E33" s="24" t="s">
-        <v>283</v>
-      </c>
-      <c r="F33" s="18"/>
+      <c r="E33" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="F33" s="28"/>
       <c r="L33" s="1" t="s">
         <v>145</v>
       </c>
@@ -2379,21 +2418,21 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="14" t="s">
+      <c r="C34" s="28"/>
+      <c r="D34" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="10" t="s">
-        <v>280</v>
-      </c>
-      <c r="F34" s="18"/>
+      <c r="E34" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="F34" s="28"/>
       <c r="L34" s="1" t="s">
         <v>149</v>
       </c>
@@ -2408,29 +2447,29 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A35" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="F35" s="18" t="s">
-        <v>233</v>
+      <c r="E35" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>232</v>
       </c>
       <c r="H35" t="s">
         <v>158</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="5" t="s">
         <v>158</v>
       </c>
       <c r="L35" s="1" t="s">
@@ -2448,25 +2487,26 @@
       <c r="P35" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="Q35" s="23" t="s">
+      <c r="Q35" s="10" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A36" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="18" t="s">
         <v>212</v>
       </c>
-      <c r="F36" s="18" t="s">
-        <v>234</v>
+      <c r="E36" s="29"/>
+      <c r="F36" s="9" t="s">
+        <v>233</v>
       </c>
       <c r="H36" t="s">
         <v>164</v>
@@ -2486,24 +2526,25 @@
       <c r="P36" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="Q36" s="23" t="s">
+      <c r="Q36" s="10" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A37" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="F37" s="18"/>
+      <c r="D37" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
       <c r="I37" t="s">
         <v>169</v>
       </c>
@@ -2519,24 +2560,24 @@
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A38" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="23" t="s">
-        <v>267</v>
-      </c>
-      <c r="F38" s="18" t="s">
-        <v>235</v>
+      <c r="E38" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>234</v>
       </c>
       <c r="H38" t="s">
         <v>175</v>
@@ -2559,24 +2600,25 @@
       <c r="P38" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="Q38" s="23" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="Q38" s="10" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A39" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="D39" s="15" t="s">
-        <v>250</v>
-      </c>
-      <c r="F39" s="18"/>
+      <c r="D39" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
       <c r="I39" t="s">
         <v>182</v>
       </c>
@@ -2596,24 +2638,24 @@
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A40" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="14" t="s">
+      <c r="D40" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="24" t="s">
-        <v>270</v>
-      </c>
-      <c r="F40" s="18" t="s">
-        <v>236</v>
+      <c r="E40" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="H40" t="s">
         <v>188</v>
@@ -2636,28 +2678,28 @@
       <c r="P40" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="Q40" s="24" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
+      <c r="Q40" s="11" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A41" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="E41" s="24" t="s">
-        <v>271</v>
-      </c>
-      <c r="F41" s="18" t="s">
-        <v>237</v>
+      <c r="E41" s="17" t="s">
+        <v>270</v>
+      </c>
+      <c r="F41" s="17" t="s">
+        <v>236</v>
       </c>
       <c r="H41" t="s">
         <v>195</v>
@@ -2681,19 +2723,20 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A42" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="14" t="s">
+      <c r="C42" s="28"/>
+      <c r="D42" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="F42" s="18" t="s">
-        <v>238</v>
+      <c r="E42" s="29"/>
+      <c r="F42" s="9" t="s">
+        <v>237</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>196</v>
@@ -2710,26 +2753,26 @@
       <c r="P42" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="Q42" s="23" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
+      <c r="Q42" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A43" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="16"/>
-      <c r="E43" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="F43" s="18" t="s">
-        <v>239</v>
+      <c r="D43" s="28"/>
+      <c r="E43" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="F43" s="17" t="s">
+        <v>238</v>
       </c>
       <c r="H43" t="s">
         <v>206</v>
@@ -2747,419 +2790,419 @@
         <v>205</v>
       </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="23" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="9"/>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="L44" s="3"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="9"/>
-      <c r="B45" s="10"/>
-      <c r="C45" s="10"/>
-      <c r="D45" s="11" t="s">
+      <c r="Q43" s="10" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="7"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A45" s="7"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="M45" s="10"/>
-      <c r="N45" s="10"/>
-      <c r="O45" s="10"/>
-      <c r="P45" s="10"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A46" s="9"/>
-      <c r="B46" s="10"/>
-      <c r="C46" s="10"/>
-      <c r="D46" s="12" t="s">
+      <c r="M45" s="8"/>
+      <c r="N45" s="8"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A46" s="7"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A47" s="9"/>
-      <c r="B47" s="10"/>
-      <c r="C47" s="10"/>
-      <c r="D47" s="12" t="s">
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A47" s="7"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="M47" s="10"/>
-      <c r="N47" s="10"/>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A48" s="9"/>
-      <c r="B48" s="10"/>
-      <c r="C48" s="10"/>
-      <c r="D48" s="12" t="s">
+      <c r="M47" s="8"/>
+      <c r="N47" s="8"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="8"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A48" s="7"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A49" s="9"/>
-      <c r="B49" s="10"/>
-      <c r="C49" s="10"/>
-      <c r="D49" s="12" t="s">
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A49" s="7"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="M49" s="10"/>
-      <c r="N49" s="10"/>
-      <c r="O49" s="10"/>
-      <c r="P49" s="10"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A50" s="9"/>
-      <c r="B50" s="10"/>
-      <c r="C50" s="10"/>
-      <c r="D50" s="12" t="s">
+      <c r="M49" s="8"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8"/>
+      <c r="P49" s="8"/>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A50" s="7"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="M50" s="10"/>
-      <c r="N50" s="10"/>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A51" s="9"/>
-      <c r="B51" s="10"/>
-      <c r="C51" s="10"/>
-      <c r="D51" s="12" t="s">
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A51" s="7"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="M51" s="10"/>
-      <c r="N51" s="10"/>
-      <c r="O51" s="10"/>
-      <c r="P51" s="10"/>
-    </row>
-    <row r="52" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="9"/>
-      <c r="B52" s="10"/>
-      <c r="C52" s="10"/>
-      <c r="D52" s="13" t="s">
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
+    </row>
+    <row r="52" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="7"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="M52" s="10"/>
-      <c r="N52" s="10"/>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A53" s="9"/>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-      <c r="D53" s="15" t="s">
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A53" s="7"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A54" s="7"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A54" s="9"/>
-      <c r="B54" s="10"/>
-      <c r="C54" s="10"/>
-      <c r="D54" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="L54" s="5"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A55" s="9"/>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="15" t="s">
+      <c r="L54" s="4"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A55" s="7"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A56" s="7"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="M55" s="10"/>
-      <c r="N55" s="10"/>
-      <c r="O55" s="10"/>
-      <c r="P55" s="10"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A56" s="9"/>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="M56" s="10"/>
-      <c r="N56" s="10"/>
-      <c r="O56" s="10"/>
-      <c r="P56" s="10"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A57" s="9"/>
-      <c r="B57" s="10"/>
-      <c r="C57" s="10"/>
-      <c r="M57" s="10"/>
-      <c r="N57" s="10"/>
-      <c r="O57" s="10"/>
-      <c r="P57" s="10"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A58" s="9"/>
-      <c r="B58" s="10"/>
-      <c r="C58" s="10"/>
-      <c r="M58" s="10"/>
-      <c r="N58" s="10"/>
-      <c r="O58" s="10"/>
-      <c r="P58" s="10"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="M59" s="10"/>
-      <c r="N59" s="10"/>
-      <c r="O59" s="10"/>
-      <c r="P59" s="10"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
-      <c r="B60" s="10"/>
-      <c r="C60" s="10"/>
-      <c r="M60" s="10"/>
-      <c r="N60" s="10"/>
-      <c r="O60" s="10"/>
-      <c r="P60" s="10"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A61" s="9"/>
-      <c r="B61" s="10"/>
-      <c r="C61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A62" s="9"/>
-      <c r="B62" s="10"/>
-      <c r="C62" s="10"/>
-      <c r="M62" s="10"/>
-      <c r="N62" s="10"/>
-      <c r="O62" s="10"/>
-      <c r="P62" s="10"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A63" s="9"/>
-      <c r="B63" s="10"/>
-      <c r="C63" s="10"/>
-      <c r="M63" s="10"/>
-      <c r="N63" s="10"/>
-      <c r="O63" s="10"/>
-      <c r="P63" s="10"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A64" s="9"/>
-      <c r="B64" s="10"/>
-      <c r="C64" s="10"/>
-      <c r="M64" s="10"/>
-      <c r="N64" s="10"/>
-      <c r="O64" s="10"/>
-      <c r="P64" s="10"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A65" s="9"/>
-      <c r="B65" s="10"/>
-      <c r="C65" s="10"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A66" s="9"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="M66" s="10"/>
-      <c r="N66" s="10"/>
-      <c r="O66" s="10"/>
-      <c r="P66" s="10"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A67" s="9"/>
-      <c r="B67" s="10"/>
-      <c r="C67" s="10"/>
-      <c r="M67" s="10"/>
-      <c r="N67" s="10"/>
-      <c r="O67" s="10"/>
-      <c r="P67" s="10"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A68" s="9"/>
-      <c r="B68" s="10"/>
-      <c r="C68" s="10"/>
-      <c r="M68" s="10"/>
-      <c r="N68" s="10"/>
-      <c r="O68" s="10"/>
-      <c r="P68" s="10"/>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A69" s="9"/>
-      <c r="B69" s="10"/>
-      <c r="C69" s="10"/>
-      <c r="M69" s="10"/>
-      <c r="N69" s="10"/>
-      <c r="O69" s="10"/>
-      <c r="P69" s="10"/>
-    </row>
-    <row r="87" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L87" s="3"/>
-    </row>
-    <row r="97" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L97" s="5"/>
-    </row>
-    <row r="130" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L130" s="3"/>
-    </row>
-    <row r="140" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L140" s="5"/>
-    </row>
-    <row r="173" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L173" s="3"/>
-    </row>
-    <row r="183" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L183" s="5"/>
-    </row>
-    <row r="216" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L216" s="3"/>
-    </row>
-    <row r="226" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L226" s="5"/>
-    </row>
-    <row r="259" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L259" s="3"/>
-    </row>
-    <row r="269" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L269" s="5"/>
-    </row>
-    <row r="302" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L302" s="3"/>
-    </row>
-    <row r="312" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L312" s="5"/>
-    </row>
-    <row r="345" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L345" s="3"/>
-    </row>
-    <row r="355" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L355" s="5"/>
-    </row>
-    <row r="388" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L388" s="3"/>
-    </row>
-    <row r="398" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L398" s="5"/>
-    </row>
-    <row r="431" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L431" s="3"/>
-    </row>
-    <row r="441" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L441" s="5"/>
-    </row>
-    <row r="474" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L474" s="3"/>
-    </row>
-    <row r="484" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L484" s="5"/>
-    </row>
-    <row r="517" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L517" s="3"/>
-    </row>
-    <row r="527" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L527" s="5"/>
-    </row>
-    <row r="560" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L560" s="3"/>
-    </row>
-    <row r="570" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L570" s="5"/>
-    </row>
-    <row r="603" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L603" s="3"/>
-    </row>
-    <row r="613" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L613" s="5"/>
-    </row>
-    <row r="646" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L646" s="3"/>
-    </row>
-    <row r="656" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L656" s="5"/>
-    </row>
-    <row r="689" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L689" s="3"/>
-    </row>
-    <row r="699" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L699" s="5"/>
-    </row>
-    <row r="732" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L732" s="3"/>
-    </row>
-    <row r="742" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L742" s="5"/>
-    </row>
-    <row r="775" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L775" s="3"/>
-    </row>
-    <row r="785" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L785" s="5"/>
-    </row>
-    <row r="818" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L818" s="3"/>
-    </row>
-    <row r="828" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L828" s="5"/>
-    </row>
-    <row r="861" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L861" s="3"/>
-    </row>
-    <row r="871" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L871" s="5"/>
-    </row>
-    <row r="904" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L904" s="3"/>
-    </row>
-    <row r="914" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L914" s="5"/>
-    </row>
-    <row r="947" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L947" s="3"/>
-    </row>
-    <row r="957" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L957" s="5"/>
-    </row>
-    <row r="990" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L990" s="3"/>
-    </row>
-    <row r="1000" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L1000" s="5"/>
-    </row>
-    <row r="1033" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L1033" s="3"/>
-    </row>
-    <row r="1043" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L1043" s="5"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A57" s="7"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A58" s="7"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A59" s="7"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A60" s="7"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="M60" s="8"/>
+      <c r="N60" s="8"/>
+      <c r="O60" s="8"/>
+      <c r="P60" s="8"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A61" s="7"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="M61" s="8"/>
+      <c r="N61" s="8"/>
+      <c r="O61" s="8"/>
+      <c r="P61" s="8"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A62" s="7"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="8"/>
+      <c r="O62" s="8"/>
+      <c r="P62" s="8"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A63" s="7"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="M63" s="8"/>
+      <c r="N63" s="8"/>
+      <c r="O63" s="8"/>
+      <c r="P63" s="8"/>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A64" s="7"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="M64" s="8"/>
+      <c r="N64" s="8"/>
+      <c r="O64" s="8"/>
+      <c r="P64" s="8"/>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A65" s="7"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="M65" s="8"/>
+      <c r="N65" s="8"/>
+      <c r="O65" s="8"/>
+      <c r="P65" s="8"/>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A66" s="7"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="M66" s="8"/>
+      <c r="N66" s="8"/>
+      <c r="O66" s="8"/>
+      <c r="P66" s="8"/>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A67" s="7"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="M67" s="8"/>
+      <c r="N67" s="8"/>
+      <c r="O67" s="8"/>
+      <c r="P67" s="8"/>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A68" s="7"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="M68" s="8"/>
+      <c r="N68" s="8"/>
+      <c r="O68" s="8"/>
+      <c r="P68" s="8"/>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A69" s="7"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="M69" s="8"/>
+      <c r="N69" s="8"/>
+      <c r="O69" s="8"/>
+      <c r="P69" s="8"/>
+    </row>
+    <row r="87" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="2"/>
+    </row>
+    <row r="97" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="4"/>
+    </row>
+    <row r="130" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L130" s="2"/>
+    </row>
+    <row r="140" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L140" s="4"/>
+    </row>
+    <row r="173" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L173" s="2"/>
+    </row>
+    <row r="183" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L183" s="4"/>
+    </row>
+    <row r="216" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L216" s="2"/>
+    </row>
+    <row r="226" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L226" s="4"/>
+    </row>
+    <row r="259" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L259" s="2"/>
+    </row>
+    <row r="269" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L269" s="4"/>
+    </row>
+    <row r="302" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L302" s="2"/>
+    </row>
+    <row r="312" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L312" s="4"/>
+    </row>
+    <row r="345" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L345" s="2"/>
+    </row>
+    <row r="355" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L355" s="4"/>
+    </row>
+    <row r="388" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L388" s="2"/>
+    </row>
+    <row r="398" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L398" s="4"/>
+    </row>
+    <row r="431" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L431" s="2"/>
+    </row>
+    <row r="441" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L441" s="4"/>
+    </row>
+    <row r="474" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L474" s="2"/>
+    </row>
+    <row r="484" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L484" s="4"/>
+    </row>
+    <row r="517" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L517" s="2"/>
+    </row>
+    <row r="527" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L527" s="4"/>
+    </row>
+    <row r="560" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L560" s="2"/>
+    </row>
+    <row r="570" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L570" s="4"/>
+    </row>
+    <row r="603" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L603" s="2"/>
+    </row>
+    <row r="613" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L613" s="4"/>
+    </row>
+    <row r="646" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L646" s="2"/>
+    </row>
+    <row r="656" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L656" s="4"/>
+    </row>
+    <row r="689" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L689" s="2"/>
+    </row>
+    <row r="699" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L699" s="4"/>
+    </row>
+    <row r="732" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L732" s="2"/>
+    </row>
+    <row r="742" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L742" s="4"/>
+    </row>
+    <row r="775" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L775" s="2"/>
+    </row>
+    <row r="785" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L785" s="4"/>
+    </row>
+    <row r="818" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L818" s="2"/>
+    </row>
+    <row r="828" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L828" s="4"/>
+    </row>
+    <row r="861" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L861" s="2"/>
+    </row>
+    <row r="871" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L871" s="4"/>
+    </row>
+    <row r="904" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L904" s="2"/>
+    </row>
+    <row r="914" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L914" s="4"/>
+    </row>
+    <row r="947" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L947" s="2"/>
+    </row>
+    <row r="957" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L957" s="4"/>
+    </row>
+    <row r="990" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L990" s="2"/>
+    </row>
+    <row r="1000" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L1000" s="4"/>
+    </row>
+    <row r="1033" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L1033" s="2"/>
+    </row>
+    <row r="1043" spans="12:12" x14ac:dyDescent="0.2">
+      <c r="L1043" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -1097,7 +1097,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1124,23 +1124,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1161,9 +1157,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1376,7 +1369,7 @@
   <cols>
     <col min="1" max="1" width="41.1640625" customWidth="1"/>
     <col min="2" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="13" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
     <col min="5" max="6" width="17.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" customWidth="1"/>
     <col min="9" max="9" width="13.5" customWidth="1"/>
@@ -1387,63 +1380,63 @@
     <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="23" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:17" s="21" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="24" t="s">
+      <c r="L1" s="22" t="s">
         <v>239</v>
       </c>
-      <c r="M1" s="24" t="s">
+      <c r="M1" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="N1" s="24" t="s">
+      <c r="N1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="24" t="s">
+      <c r="O1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="24" t="s">
+      <c r="P1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="25" t="s">
+      <c r="Q1" s="23" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="18" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="28"/>
+      <c r="F2" s="25"/>
       <c r="H2" t="s">
         <v>11</v>
       </c>
@@ -1462,18 +1455,18 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="18" t="s">
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="F3" s="28"/>
+      <c r="F3" s="25"/>
       <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
@@ -1492,16 +1485,16 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="18" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
       <c r="L4" s="1" t="s">
         <v>16</v>
       </c>
@@ -1517,16 +1510,16 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="18" t="s">
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
       <c r="L5" s="1" t="s">
         <v>19</v>
       </c>
@@ -1542,20 +1535,20 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="18" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="16" t="s">
         <v>221</v>
       </c>
       <c r="L6" s="1" t="s">
@@ -1573,18 +1566,18 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="18" t="s">
+      <c r="C7" s="25"/>
+      <c r="D7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
       <c r="L7" s="1" t="s">
         <v>26</v>
       </c>
@@ -1596,16 +1589,16 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="18" t="s">
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
       <c r="L8" s="1" t="s">
         <v>28</v>
       </c>
@@ -1617,17 +1610,17 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="18" t="s">
+      <c r="C9" s="25"/>
+      <c r="D9" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="29"/>
+      <c r="E9" s="26"/>
       <c r="F9" s="9" t="s">
         <v>222</v>
       </c>
@@ -1646,20 +1639,20 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="18" t="s">
+      <c r="C10" s="25"/>
+      <c r="D10" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="F10" s="28"/>
+      <c r="F10" s="25"/>
       <c r="L10" s="1" t="s">
         <v>33</v>
       </c>
@@ -1675,18 +1668,18 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="18" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="16" t="s">
         <v>37</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="29"/>
+      <c r="F11" s="26"/>
       <c r="I11" t="s">
         <v>208</v>
       </c>
@@ -1703,22 +1696,22 @@
       <c r="P11" s="4"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F12" s="16" t="s">
         <v>223</v>
       </c>
       <c r="L12" s="1" t="s">
@@ -1736,18 +1729,18 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="18" t="s">
+      <c r="C13" s="25"/>
+      <c r="D13" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
       <c r="M13" s="1" t="s">
         <v>47</v>
       </c>
@@ -1760,20 +1753,20 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="25"/>
+      <c r="D14" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="F14" s="28"/>
+      <c r="F14" s="25"/>
       <c r="L14" s="1" t="s">
         <v>49</v>
       </c>
@@ -1789,18 +1782,18 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="18" t="s">
+      <c r="C15" s="25"/>
+      <c r="D15" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
       <c r="M15" s="1" t="s">
         <v>55</v>
       </c>
@@ -1813,20 +1806,20 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="18" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="F16" s="28"/>
+      <c r="F16" s="25"/>
       <c r="L16" s="1" t="s">
         <v>57</v>
       </c>
@@ -1842,20 +1835,20 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="25"/>
+      <c r="D17" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="F17" s="28"/>
+      <c r="F17" s="25"/>
       <c r="L17" s="1" t="s">
         <v>61</v>
       </c>
@@ -1871,20 +1864,20 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="18" t="s">
+      <c r="C18" s="25"/>
+      <c r="D18" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="F18" s="28"/>
+      <c r="F18" s="25"/>
       <c r="L18" s="1" t="s">
         <v>65</v>
       </c>
@@ -1900,22 +1893,22 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="17" t="s">
+      <c r="F19" s="16" t="s">
         <v>224</v>
       </c>
       <c r="H19" t="s">
@@ -1944,19 +1937,19 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="C20" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="E20" s="29"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="9" t="s">
         <v>225</v>
       </c>
@@ -1983,20 +1976,20 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
       <c r="I21" t="s">
         <v>86</v>
       </c>
@@ -2017,22 +2010,22 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="F22" s="16" t="s">
         <v>226</v>
       </c>
       <c r="H22" t="s">
@@ -2061,20 +2054,20 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
       <c r="I23" t="s">
         <v>99</v>
       </c>
@@ -2095,22 +2088,22 @@
       </c>
     </row>
     <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="16" t="s">
         <v>227</v>
       </c>
       <c r="H24" t="s">
@@ -2139,22 +2132,22 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="16" t="s">
         <v>228</v>
       </c>
       <c r="H25" t="s">
@@ -2180,17 +2173,17 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="28"/>
-      <c r="D26" s="18" t="s">
+      <c r="C26" s="25"/>
+      <c r="D26" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="29"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="9" t="s">
         <v>229</v>
       </c>
@@ -2214,20 +2207,20 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="17" t="s">
+      <c r="C27" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="28"/>
-      <c r="E27" s="17" t="s">
+      <c r="D27" s="25"/>
+      <c r="E27" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="F27" s="17" t="s">
+      <c r="F27" s="16" t="s">
         <v>230</v>
       </c>
       <c r="H27" t="s">
@@ -2251,22 +2244,22 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="16" t="s">
         <v>231</v>
       </c>
       <c r="L28" s="1" t="s">
@@ -2284,18 +2277,18 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" s="19" t="s">
+      <c r="A29" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="18" t="s">
+      <c r="C29" s="25"/>
+      <c r="D29" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
       <c r="M29" s="1" t="s">
         <v>131</v>
       </c>
@@ -2308,20 +2301,20 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="18" t="s">
+      <c r="C30" s="25"/>
+      <c r="D30" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="F30" s="28"/>
+      <c r="F30" s="25"/>
       <c r="L30" s="1" t="s">
         <v>133</v>
       </c>
@@ -2337,18 +2330,18 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" s="19" t="s">
+      <c r="A31" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="18" t="s">
+      <c r="C31" s="25"/>
+      <c r="D31" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
       <c r="M31" s="1" t="s">
         <v>139</v>
       </c>
@@ -2361,20 +2354,20 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="18" t="s">
+      <c r="C32" s="25"/>
+      <c r="D32" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="F32" s="28"/>
+      <c r="F32" s="25"/>
       <c r="L32" s="1" t="s">
         <v>141</v>
       </c>
@@ -2390,20 +2383,20 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="C33" s="28"/>
-      <c r="D33" s="18" t="s">
+      <c r="C33" s="25"/>
+      <c r="D33" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="F33" s="28"/>
+      <c r="F33" s="25"/>
       <c r="L33" s="1" t="s">
         <v>145</v>
       </c>
@@ -2419,20 +2412,20 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="18" t="s">
+      <c r="C34" s="25"/>
+      <c r="D34" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="F34" s="28"/>
+      <c r="F34" s="25"/>
       <c r="L34" s="1" t="s">
         <v>149</v>
       </c>
@@ -2448,22 +2441,22 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="16" t="s">
         <v>232</v>
       </c>
       <c r="H35" t="s">
@@ -2492,19 +2485,19 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="29"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="9" t="s">
         <v>233</v>
       </c>
@@ -2531,20 +2524,20 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" s="22" t="s">
+      <c r="A37" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
       <c r="I37" t="s">
         <v>169</v>
       </c>
@@ -2561,22 +2554,22 @@
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38" s="33" t="s">
+      <c r="A38" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="16" t="s">
         <v>234</v>
       </c>
       <c r="H38" t="s">
@@ -2605,20 +2598,20 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" s="22" t="s">
+      <c r="A39" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="C39" s="17" t="s">
+      <c r="C39" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
       <c r="I39" t="s">
         <v>182</v>
       </c>
@@ -2639,22 +2632,22 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" s="31" t="s">
+      <c r="A40" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="16" t="s">
         <v>235</v>
       </c>
       <c r="H40" t="s">
@@ -2683,22 +2676,22 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="F41" s="16" t="s">
         <v>236</v>
       </c>
       <c r="H41" t="s">
@@ -2724,17 +2717,17 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A42" s="22" t="s">
+      <c r="A42" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="C42" s="28"/>
-      <c r="D42" s="18" t="s">
+      <c r="C42" s="25"/>
+      <c r="D42" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="29"/>
+      <c r="E42" s="26"/>
       <c r="F42" s="9" t="s">
         <v>237</v>
       </c>
@@ -2758,20 +2751,20 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A43" s="22" t="s">
+      <c r="A43" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="17" t="s">
+      <c r="C43" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="28"/>
-      <c r="E43" s="17" t="s">
+      <c r="D43" s="25"/>
+      <c r="E43" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="F43" s="17" t="s">
+      <c r="F43" s="16" t="s">
         <v>238</v>
       </c>
       <c r="H43" t="s">
@@ -2808,7 +2801,7 @@
       <c r="A45" s="7"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="13" t="s">
         <v>220</v>
       </c>
       <c r="M45" s="8"/>
@@ -2820,7 +2813,7 @@
       <c r="A46" s="7"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="14" t="s">
         <v>213</v>
       </c>
       <c r="M46" s="8"/>
@@ -2832,7 +2825,7 @@
       <c r="A47" s="7"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="14" t="s">
         <v>214</v>
       </c>
       <c r="M47" s="8"/>
@@ -2844,7 +2837,7 @@
       <c r="A48" s="7"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="14" t="s">
         <v>215</v>
       </c>
       <c r="M48" s="8"/>
@@ -2856,7 +2849,7 @@
       <c r="A49" s="7"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="14" t="s">
         <v>216</v>
       </c>
       <c r="M49" s="8"/>
@@ -2868,7 +2861,7 @@
       <c r="A50" s="7"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="14" t="s">
         <v>217</v>
       </c>
       <c r="M50" s="8"/>
@@ -2880,7 +2873,7 @@
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
-      <c r="D51" s="15" t="s">
+      <c r="D51" s="14" t="s">
         <v>218</v>
       </c>
       <c r="M51" s="8"/>
@@ -2892,7 +2885,7 @@
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="15" t="s">
         <v>219</v>
       </c>
       <c r="M52" s="8"/>

--- a/data/translation_table.xlsx
+++ b/data/translation_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosesharifi/Documents/GitHub/TeamProject/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\perla\Documents\AT\TeamProject\GitHub\TeamProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF063078-A0C0-5943-995E-168BCC65C212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CF96AA-97A0-4C81-83DA-E12A84A0487A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="840" windowWidth="12580" windowHeight="15640" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -879,14 +879,14 @@
     <t>DB4_Horst</t>
   </si>
   <si>
-    <t>DB5_Kuopio</t>
+    <t>DB5_Lavikainen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -936,15 +936,7 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -977,72 +969,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1060,117 +992,72 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1364,1838 +1251,2778 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1043"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O1043"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="41.1640625" customWidth="1"/>
-    <col min="2" max="3" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="6" width="17.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="27.33203125" customWidth="1"/>
-    <col min="14" max="14" width="15.5" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17.77734375" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.77734375" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.33203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5546875" style="19" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.21875" style="19" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.21875" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="21" customFormat="1" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:15" s="17" customFormat="1" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="J1" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="K1" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="L1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="M1" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="N1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="23" t="s">
+      <c r="O1" s="23" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="16" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="F2" s="25"/>
-      <c r="H2" t="s">
+      <c r="F2" s="9"/>
+      <c r="H2" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="J2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="K2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="L2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
+      <c r="M2" s="21"/>
+      <c r="N2" s="21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="16" t="s">
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="F3" s="25"/>
-      <c r="H3" s="3" t="s">
+      <c r="F3" s="9"/>
+      <c r="H3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="J3" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="K3" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="L3" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1" t="s">
+      <c r="M3" s="21"/>
+      <c r="N3" s="21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="16" t="s">
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="L4" s="1" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="J4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="K4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="L4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1" t="s">
+      <c r="M4" s="21"/>
+      <c r="N4" s="21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="16" t="s">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="16" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="L5" s="1" t="s">
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="J5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="K5" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="L5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1" t="s">
+      <c r="M5" s="21"/>
+      <c r="N5" s="21" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="9"/>
+      <c r="D6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="J6" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="K6" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="L6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1" t="s">
+      <c r="M6" s="21"/>
+      <c r="N6" s="21" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="9"/>
+      <c r="D7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="L7" s="1" t="s">
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="J7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1" t="s">
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="16" t="s">
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26"/>
-      <c r="L8" s="1" t="s">
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="J8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1" t="s">
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="16" t="s">
+      <c r="C9" s="9"/>
+      <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="26"/>
-      <c r="F9" s="9" t="s">
+      <c r="E9" s="10"/>
+      <c r="F9" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="J9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="K9" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="L9" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1" t="s">
+      <c r="M9" s="21"/>
+      <c r="N9" s="21" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="9"/>
+      <c r="D10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="F10" s="25"/>
-      <c r="L10" s="1" t="s">
+      <c r="F10" s="9"/>
+      <c r="J10" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="K10" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="L10" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1" t="s">
+      <c r="N10" s="21" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="16" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F11" s="26"/>
-      <c r="I11" t="s">
+      <c r="F11" s="10"/>
+      <c r="I11" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="J11" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="K11" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="N11" s="4" t="s">
+      <c r="L11" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12" s="27" t="s">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="J12" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="K12" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="L12" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1" t="s">
+      <c r="M12" s="21"/>
+      <c r="N12" s="21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="16" t="s">
+      <c r="C13" s="9"/>
+      <c r="D13" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="M13" s="1" t="s">
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="K13" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="L13" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1" t="s">
+      <c r="M13" s="21"/>
+      <c r="N13" s="21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="16" t="s">
+      <c r="C14" s="9"/>
+      <c r="D14" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="F14" s="25"/>
-      <c r="L14" s="1" t="s">
+      <c r="F14" s="9"/>
+      <c r="J14" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="K14" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="L14" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1" t="s">
+      <c r="M14" s="21"/>
+      <c r="N14" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="16" t="s">
+      <c r="C15" s="9"/>
+      <c r="D15" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="M15" s="1" t="s">
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="K15" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="L15" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1" t="s">
+      <c r="M15" s="21"/>
+      <c r="N15" s="21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="16" t="s">
+      <c r="C16" s="9"/>
+      <c r="D16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F16" s="25"/>
-      <c r="L16" s="1" t="s">
+      <c r="F16" s="9"/>
+      <c r="J16" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="K16" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="L16" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1" t="s">
+      <c r="M16" s="21"/>
+      <c r="N16" s="21" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="16" t="s">
+      <c r="C17" s="9"/>
+      <c r="D17" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="F17" s="25"/>
-      <c r="L17" s="1" t="s">
+      <c r="F17" s="9"/>
+      <c r="J17" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="K17" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="L17" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
+      <c r="M17" s="21"/>
+      <c r="N17" s="21" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="16" t="s">
+      <c r="C18" s="9"/>
+      <c r="D18" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="F18" s="25"/>
-      <c r="L18" s="1" t="s">
+      <c r="F18" s="9"/>
+      <c r="J18" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="K18" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="L18" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1" t="s">
+      <c r="M18" s="21"/>
+      <c r="N18" s="21" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" s="27" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="J19" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="K19" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="L19" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="M19" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="N19" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="Q19" s="10" t="s">
+      <c r="O19" s="21" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="9" t="s">
+      <c r="E20" s="10"/>
+      <c r="F20" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="J20" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="K20" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="L20" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="O20" s="1" t="s">
+      <c r="M20" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="N20" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="Q20" s="10" t="s">
+      <c r="O20" s="21" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E21" s="26"/>
-      <c r="F21" s="26"/>
-      <c r="I21" t="s">
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="I21" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="J21" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="K21" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="L21" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="O21" s="1" t="s">
+      <c r="M21" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="N21" s="21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22" s="27" t="s">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="J22" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="K22" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="L22" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="M22" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="N22" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="Q22" s="10" t="s">
+      <c r="O22" s="21" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="I23" t="s">
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="I23" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="J23" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="K23" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="L23" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="O23" s="1" t="s">
+      <c r="M23" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="N23" s="21" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="27" t="s">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="J24" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="K24" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="L24" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="O24" s="6" t="s">
+      <c r="M24" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="N24" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="Q24" s="11" t="s">
+      <c r="O24" s="21" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25" s="27" t="s">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="J25" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="K25" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="L25" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="M25" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="N25" s="21" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26" s="17" t="s">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="25"/>
-      <c r="D26" s="16" t="s">
+      <c r="C26" s="9"/>
+      <c r="D26" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="9" t="s">
+      <c r="E26" s="10"/>
+      <c r="F26" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="J26" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="K26" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="L26" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="O26" s="1" t="s">
+      <c r="M26" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="P26" s="1" t="s">
+      <c r="N26" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="Q26" s="10" t="s">
+      <c r="O26" s="21" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27" s="19" t="s">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="16" t="s">
+      <c r="D27" s="9"/>
+      <c r="E27" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="K27" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="N27" s="1" t="s">
+      <c r="L27" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="O27" s="1" t="s">
+      <c r="M27" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="10" t="s">
+      <c r="N27" s="21"/>
+      <c r="O27" s="21" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28" s="29" t="s">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="F28" s="16" t="s">
+      <c r="F28" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="J28" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="K28" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="L28" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1" t="s">
+      <c r="M28" s="21"/>
+      <c r="N28" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29" s="17" t="s">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="16" t="s">
+      <c r="C29" s="9"/>
+      <c r="D29" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26"/>
-      <c r="M29" s="1" t="s">
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="K29" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="N29" s="1" t="s">
+      <c r="L29" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1" t="s">
+      <c r="M29" s="21"/>
+      <c r="N29" s="21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="16" t="s">
+      <c r="C30" s="9"/>
+      <c r="D30" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="16" t="s">
+      <c r="E30" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="F30" s="25"/>
-      <c r="L30" s="1" t="s">
+      <c r="F30" s="9"/>
+      <c r="J30" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="K30" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="L30" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1" t="s">
+      <c r="M30" s="21"/>
+      <c r="N30" s="21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31" s="17" t="s">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="16" t="s">
+      <c r="C31" s="9"/>
+      <c r="D31" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26"/>
-      <c r="M31" s="1" t="s">
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="K31" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="N31" s="1" t="s">
+      <c r="L31" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1" t="s">
+      <c r="M31" s="21"/>
+      <c r="N31" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" s="17" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="16" t="s">
+      <c r="C32" s="9"/>
+      <c r="D32" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="F32" s="25"/>
-      <c r="L32" s="1" t="s">
+      <c r="F32" s="9"/>
+      <c r="J32" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="K32" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="N32" s="1" t="s">
+      <c r="L32" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1" t="s">
+      <c r="M32" s="21"/>
+      <c r="N32" s="21" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33" s="19" t="s">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="16" t="s">
+      <c r="C33" s="9"/>
+      <c r="D33" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E33" s="16" t="s">
+      <c r="E33" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="F33" s="25"/>
-      <c r="L33" s="1" t="s">
+      <c r="F33" s="9"/>
+      <c r="J33" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="K33" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="N33" s="1" t="s">
+      <c r="L33" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1" t="s">
+      <c r="M33" s="21"/>
+      <c r="N33" s="21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34" s="19" t="s">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="16" t="s">
+      <c r="C34" s="9"/>
+      <c r="D34" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="E34" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="F34" s="25"/>
-      <c r="L34" s="1" t="s">
+      <c r="F34" s="9"/>
+      <c r="J34" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="K34" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="L34" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1" t="s">
+      <c r="M34" s="21"/>
+      <c r="N34" s="21" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35" s="28" t="s">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F35" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="25" t="s">
         <v>158</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="J35" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="K35" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="N35" s="1" t="s">
+      <c r="L35" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="O35" s="1" t="s">
+      <c r="M35" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="P35" s="1" t="s">
+      <c r="N35" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="Q35" s="10" t="s">
+      <c r="O35" s="21" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" s="20" t="s">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="9" t="s">
+      <c r="E36" s="10"/>
+      <c r="F36" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="J36" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="K36" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="N36" s="1" t="s">
+      <c r="L36" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="O36" s="1" t="s">
+      <c r="M36" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="N36" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="Q36" s="10" t="s">
+      <c r="O36" s="21" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" s="20" t="s">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="I37" t="s">
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="I37" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="J37" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1" t="s">
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="P37" s="1" t="s">
+      <c r="N37" s="21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38" s="30" t="s">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="E38" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="F38" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="I38" t="s">
+      <c r="I38" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="J38" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="K38" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="N38" s="1" t="s">
+      <c r="L38" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="O38" s="1" t="s">
+      <c r="M38" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="P38" s="1" t="s">
+      <c r="N38" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="Q38" s="10" t="s">
+      <c r="O38" s="21" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" s="20" t="s">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D39" s="16" t="s">
+      <c r="D39" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="I39" t="s">
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="I39" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="L39" s="1" t="s">
+      <c r="J39" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="K39" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="N39" s="1" t="s">
+      <c r="L39" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="O39" s="1" t="s">
+      <c r="M39" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="P39" s="1" t="s">
+      <c r="N39" s="21" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" s="28" t="s">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="E40" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="F40" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="I40" t="s">
+      <c r="I40" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="J40" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="K40" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="N40" s="1" t="s">
+      <c r="L40" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="O40" s="1" t="s">
+      <c r="M40" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="P40" s="1" t="s">
+      <c r="N40" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="Q40" s="11" t="s">
+      <c r="O40" s="21" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" s="28" t="s">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
         <v>190</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="E41" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="F41" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I41" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="J41" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="K41" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="N41" s="1" t="s">
+      <c r="L41" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="O41" s="1" t="s">
+      <c r="M41" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="P41" s="1" t="s">
+      <c r="N41" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A42" s="20" t="s">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C42" s="25"/>
-      <c r="D42" s="16" t="s">
+      <c r="C42" s="9"/>
+      <c r="D42" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="9" t="s">
+      <c r="E42" s="10"/>
+      <c r="F42" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="J42" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="M42" s="1" t="s">
+      <c r="K42" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="N42" s="1" t="s">
+      <c r="L42" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="O42" s="1" t="s">
+      <c r="M42" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="P42" s="1" t="s">
+      <c r="N42" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="Q42" s="10" t="s">
+      <c r="O42" s="21" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A43" s="20" t="s">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="25"/>
-      <c r="E43" s="16" t="s">
+      <c r="D43" s="9"/>
+      <c r="E43" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="F43" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="I43" t="s">
+      <c r="I43" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="K43" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="N43" s="1" t="s">
+      <c r="L43" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="O43" s="1" t="s">
+      <c r="M43" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="10" t="s">
+      <c r="N43" s="21"/>
+      <c r="O43" s="21" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="7"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="8"/>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
-      <c r="P44" s="8"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45" s="7"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="13" t="s">
+    <row r="44" spans="1:15" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44"/>
+      <c r="E44"/>
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
+    </row>
+    <row r="45" spans="1:15" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8"/>
-      <c r="O45" s="8"/>
-      <c r="P45" s="8"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46" s="7"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="14" t="s">
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="21"/>
+    </row>
+    <row r="46" spans="1:15" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8"/>
-      <c r="O46" s="8"/>
-      <c r="P46" s="8"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A47" s="7"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="14" t="s">
+      <c r="E46"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="J46" s="21"/>
+      <c r="K46" s="21"/>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21"/>
+    </row>
+    <row r="47" spans="1:15" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="M47" s="8"/>
-      <c r="N47" s="8"/>
-      <c r="O47" s="8"/>
-      <c r="P47" s="8"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48" s="7"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="14" t="s">
+      <c r="E47"/>
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21"/>
+    </row>
+    <row r="48" spans="1:15" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8"/>
-      <c r="O48" s="8"/>
-      <c r="P48" s="8"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A49" s="7"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="14" t="s">
+      <c r="E48"/>
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="21"/>
+      <c r="L48" s="21"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="21"/>
+    </row>
+    <row r="49" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8"/>
-      <c r="O49" s="8"/>
-      <c r="P49" s="8"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A50" s="7"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="14" t="s">
+      <c r="E49"/>
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+    </row>
+    <row r="50" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-      <c r="P50" s="8"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A51" s="7"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="14" t="s">
+      <c r="E50"/>
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="21"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+    </row>
+    <row r="51" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="8"/>
-    </row>
-    <row r="52" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="7"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="15" t="s">
+      <c r="E51"/>
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="J51" s="21"/>
+      <c r="K51" s="21"/>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+    </row>
+    <row r="52" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="M52" s="8"/>
-      <c r="N52" s="8"/>
-      <c r="O52" s="8"/>
-      <c r="P52" s="8"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A53" s="7"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="12" t="s">
+      <c r="E52"/>
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="21"/>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
+    </row>
+    <row r="53" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="M53" s="8"/>
-      <c r="N53" s="8"/>
-      <c r="O53" s="8"/>
-      <c r="P53" s="8"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A54" s="7"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="12" t="s">
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="J53" s="21"/>
+      <c r="K53" s="21"/>
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="21"/>
+    </row>
+    <row r="54" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="L54" s="4"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8"/>
-      <c r="O54" s="8"/>
-      <c r="P54" s="8"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A55" s="7"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="12" t="s">
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+    </row>
+    <row r="55" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8"/>
-      <c r="O55" s="8"/>
-      <c r="P55" s="8"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A56" s="7"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="12" t="s">
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+    </row>
+    <row r="56" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8"/>
-      <c r="O56" s="8"/>
-      <c r="P56" s="8"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A57" s="7"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8"/>
-      <c r="O57" s="8"/>
-      <c r="P57" s="8"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A58" s="7"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A59" s="7"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
-      <c r="P59" s="8"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A60" s="7"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="M60" s="8"/>
-      <c r="N60" s="8"/>
-      <c r="O60" s="8"/>
-      <c r="P60" s="8"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A61" s="7"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="M61" s="8"/>
-      <c r="N61" s="8"/>
-      <c r="O61" s="8"/>
-      <c r="P61" s="8"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A62" s="7"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="M62" s="8"/>
-      <c r="N62" s="8"/>
-      <c r="O62" s="8"/>
-      <c r="P62" s="8"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A63" s="7"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="M63" s="8"/>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
-      <c r="P63" s="8"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A64" s="7"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="M64" s="8"/>
-      <c r="N64" s="8"/>
-      <c r="O64" s="8"/>
-      <c r="P64" s="8"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="M65" s="8"/>
-      <c r="N65" s="8"/>
-      <c r="O65" s="8"/>
-      <c r="P65" s="8"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A66" s="7"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="M66" s="8"/>
-      <c r="N66" s="8"/>
-      <c r="O66" s="8"/>
-      <c r="P66" s="8"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A67" s="7"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="M67" s="8"/>
-      <c r="N67" s="8"/>
-      <c r="O67" s="8"/>
-      <c r="P67" s="8"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A68" s="7"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="M68" s="8"/>
-      <c r="N68" s="8"/>
-      <c r="O68" s="8"/>
-      <c r="P68" s="8"/>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A69" s="7"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="M69" s="8"/>
-      <c r="N69" s="8"/>
-      <c r="O69" s="8"/>
-      <c r="P69" s="8"/>
-    </row>
-    <row r="87" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L87" s="2"/>
-    </row>
-    <row r="97" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L97" s="4"/>
-    </row>
-    <row r="130" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L130" s="2"/>
-    </row>
-    <row r="140" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L140" s="4"/>
-    </row>
-    <row r="173" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L173" s="2"/>
-    </row>
-    <row r="183" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L183" s="4"/>
-    </row>
-    <row r="216" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L216" s="2"/>
-    </row>
-    <row r="226" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L226" s="4"/>
-    </row>
-    <row r="259" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L259" s="2"/>
-    </row>
-    <row r="269" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L269" s="4"/>
-    </row>
-    <row r="302" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L302" s="2"/>
-    </row>
-    <row r="312" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L312" s="4"/>
-    </row>
-    <row r="345" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L345" s="2"/>
-    </row>
-    <row r="355" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L355" s="4"/>
-    </row>
-    <row r="388" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L388" s="2"/>
-    </row>
-    <row r="398" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L398" s="4"/>
-    </row>
-    <row r="431" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L431" s="2"/>
-    </row>
-    <row r="441" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L441" s="4"/>
-    </row>
-    <row r="474" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L474" s="2"/>
-    </row>
-    <row r="484" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L484" s="4"/>
-    </row>
-    <row r="517" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L517" s="2"/>
-    </row>
-    <row r="527" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L527" s="4"/>
-    </row>
-    <row r="560" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L560" s="2"/>
-    </row>
-    <row r="570" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L570" s="4"/>
-    </row>
-    <row r="603" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L603" s="2"/>
-    </row>
-    <row r="613" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L613" s="4"/>
-    </row>
-    <row r="646" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L646" s="2"/>
-    </row>
-    <row r="656" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L656" s="4"/>
-    </row>
-    <row r="689" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L689" s="2"/>
-    </row>
-    <row r="699" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L699" s="4"/>
-    </row>
-    <row r="732" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L732" s="2"/>
-    </row>
-    <row r="742" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L742" s="4"/>
-    </row>
-    <row r="775" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L775" s="2"/>
-    </row>
-    <row r="785" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L785" s="4"/>
-    </row>
-    <row r="818" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L818" s="2"/>
-    </row>
-    <row r="828" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L828" s="4"/>
-    </row>
-    <row r="861" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L861" s="2"/>
-    </row>
-    <row r="871" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L871" s="4"/>
-    </row>
-    <row r="904" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L904" s="2"/>
-    </row>
-    <row r="914" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L914" s="4"/>
-    </row>
-    <row r="947" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L947" s="2"/>
-    </row>
-    <row r="957" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L957" s="4"/>
-    </row>
-    <row r="990" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L990" s="2"/>
-    </row>
-    <row r="1000" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L1000" s="4"/>
-    </row>
-    <row r="1033" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L1033" s="2"/>
-    </row>
-    <row r="1043" spans="12:12" x14ac:dyDescent="0.2">
-      <c r="L1043" s="4"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="21"/>
+      <c r="L56" s="21"/>
+      <c r="M56" s="21"/>
+      <c r="N56" s="21"/>
+    </row>
+    <row r="57" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="21"/>
+      <c r="L57" s="21"/>
+      <c r="M57" s="21"/>
+      <c r="N57" s="21"/>
+    </row>
+    <row r="58" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="21"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
+    </row>
+    <row r="59" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59"/>
+      <c r="E59"/>
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="21"/>
+      <c r="L59" s="21"/>
+      <c r="M59" s="21"/>
+      <c r="N59" s="21"/>
+    </row>
+    <row r="60" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60"/>
+      <c r="E60"/>
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
+    </row>
+    <row r="61" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61"/>
+      <c r="E61"/>
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="21"/>
+      <c r="L61" s="21"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
+    </row>
+    <row r="62" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62"/>
+      <c r="E62"/>
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="21"/>
+      <c r="M62" s="21"/>
+      <c r="N62" s="21"/>
+    </row>
+    <row r="63" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63"/>
+      <c r="E63"/>
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="J63" s="21"/>
+      <c r="K63" s="21"/>
+      <c r="L63" s="21"/>
+      <c r="M63" s="21"/>
+      <c r="N63" s="21"/>
+    </row>
+    <row r="64" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64"/>
+      <c r="E64"/>
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21"/>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21"/>
+    </row>
+    <row r="65" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65"/>
+      <c r="E65"/>
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="J65" s="21"/>
+      <c r="K65" s="21"/>
+      <c r="L65" s="21"/>
+      <c r="M65" s="21"/>
+      <c r="N65" s="21"/>
+    </row>
+    <row r="66" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="1"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66"/>
+      <c r="E66"/>
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="J66" s="21"/>
+      <c r="K66" s="21"/>
+      <c r="L66" s="21"/>
+      <c r="M66" s="21"/>
+      <c r="N66" s="21"/>
+    </row>
+    <row r="67" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67"/>
+      <c r="E67"/>
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="21"/>
+      <c r="M67" s="21"/>
+      <c r="N67" s="21"/>
+    </row>
+    <row r="68" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+    </row>
+    <row r="69" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="1"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="21"/>
+      <c r="M69" s="21"/>
+      <c r="N69" s="21"/>
+    </row>
+    <row r="70" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70"/>
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="J70" s="21"/>
+    </row>
+    <row r="71" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71"/>
+      <c r="D71"/>
+      <c r="E71"/>
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="J71" s="21"/>
+    </row>
+    <row r="72" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72"/>
+      <c r="D72"/>
+      <c r="E72"/>
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="J72" s="21"/>
+    </row>
+    <row r="73" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73"/>
+      <c r="D73"/>
+      <c r="E73"/>
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="J73" s="21"/>
+    </row>
+    <row r="74" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74"/>
+      <c r="D74"/>
+      <c r="E74"/>
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="J74" s="21"/>
+    </row>
+    <row r="75" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75"/>
+      <c r="D75"/>
+      <c r="E75"/>
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="J75" s="21"/>
+    </row>
+    <row r="76" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76"/>
+      <c r="D76"/>
+      <c r="E76"/>
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="J76" s="21"/>
+    </row>
+    <row r="77" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77"/>
+      <c r="D77"/>
+      <c r="E77"/>
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="J77" s="21"/>
+    </row>
+    <row r="78" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78"/>
+      <c r="D78"/>
+      <c r="E78"/>
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="J78" s="21"/>
+    </row>
+    <row r="79" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79"/>
+      <c r="D79"/>
+      <c r="E79"/>
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="J79" s="21"/>
+    </row>
+    <row r="80" spans="1:14" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80"/>
+      <c r="D80"/>
+      <c r="E80"/>
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="J80" s="21"/>
+    </row>
+    <row r="81" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81"/>
+      <c r="D81"/>
+      <c r="E81"/>
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="J81" s="21"/>
+    </row>
+    <row r="82" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82"/>
+      <c r="D82"/>
+      <c r="E82"/>
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="J82" s="21"/>
+    </row>
+    <row r="83" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83"/>
+      <c r="D83"/>
+      <c r="E83"/>
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="J83" s="21"/>
+    </row>
+    <row r="84" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84"/>
+      <c r="D84"/>
+      <c r="E84"/>
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="J84" s="21"/>
+    </row>
+    <row r="85" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85"/>
+      <c r="D85"/>
+      <c r="E85"/>
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="J85" s="21"/>
+    </row>
+    <row r="86" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="J86" s="21"/>
+    </row>
+    <row r="87" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="J87" s="20"/>
+    </row>
+    <row r="88" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88"/>
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="J88" s="21"/>
+    </row>
+    <row r="89" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89"/>
+      <c r="D89"/>
+      <c r="E89"/>
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="J89" s="21"/>
+    </row>
+    <row r="90" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90"/>
+      <c r="D90"/>
+      <c r="E90"/>
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="J90" s="21"/>
+    </row>
+    <row r="91" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91"/>
+      <c r="D91"/>
+      <c r="E91"/>
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="J91" s="21"/>
+    </row>
+    <row r="92" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92"/>
+      <c r="D92"/>
+      <c r="E92"/>
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="J92" s="21"/>
+    </row>
+    <row r="93" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93"/>
+      <c r="D93"/>
+      <c r="E93"/>
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="J93" s="21"/>
+    </row>
+    <row r="94" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94"/>
+      <c r="D94"/>
+      <c r="E94"/>
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="J94" s="21"/>
+    </row>
+    <row r="95" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95"/>
+      <c r="D95"/>
+      <c r="E95"/>
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="J95" s="21"/>
+    </row>
+    <row r="96" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96"/>
+      <c r="D96"/>
+      <c r="E96"/>
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="J96" s="21"/>
+    </row>
+    <row r="97" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97"/>
+      <c r="D97"/>
+      <c r="E97"/>
+      <c r="F97"/>
+      <c r="G97"/>
+    </row>
+    <row r="98" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98"/>
+      <c r="D98"/>
+      <c r="E98"/>
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="J98" s="21"/>
+    </row>
+    <row r="99" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="J99" s="21"/>
+    </row>
+    <row r="100" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="J100" s="21"/>
+    </row>
+    <row r="101" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="J101" s="21"/>
+    </row>
+    <row r="102" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="J102" s="21"/>
+    </row>
+    <row r="103" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="J103" s="21"/>
+    </row>
+    <row r="104" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="J104" s="21"/>
+    </row>
+    <row r="105" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="J105" s="21"/>
+    </row>
+    <row r="106" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="J106" s="21"/>
+    </row>
+    <row r="107" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="J107" s="21"/>
+    </row>
+    <row r="108" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="J108" s="21"/>
+    </row>
+    <row r="109" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="J109" s="21"/>
+    </row>
+    <row r="110" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="J110" s="21"/>
+    </row>
+    <row r="111" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="J111" s="21"/>
+    </row>
+    <row r="112" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="J112" s="21"/>
+    </row>
+    <row r="113" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="J113" s="21"/>
+    </row>
+    <row r="114" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="J114" s="21"/>
+    </row>
+    <row r="115" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="J115" s="21"/>
+    </row>
+    <row r="116" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="J116" s="21"/>
+    </row>
+    <row r="117" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="J117" s="21"/>
+    </row>
+    <row r="118" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="J118" s="21"/>
+    </row>
+    <row r="119" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="J119" s="21"/>
+    </row>
+    <row r="120" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="J120" s="21"/>
+    </row>
+    <row r="121" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="J121" s="21"/>
+    </row>
+    <row r="122" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="J122" s="21"/>
+    </row>
+    <row r="123" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="J123" s="21"/>
+    </row>
+    <row r="124" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="J124" s="21"/>
+    </row>
+    <row r="125" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="J125" s="21"/>
+    </row>
+    <row r="126" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="J126" s="21"/>
+    </row>
+    <row r="127" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="J127" s="21"/>
+    </row>
+    <row r="128" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="J128" s="21"/>
+    </row>
+    <row r="129" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="J129" s="21"/>
+    </row>
+    <row r="130" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="J130" s="20"/>
+    </row>
+    <row r="131" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="J131" s="21"/>
+    </row>
+    <row r="132" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="J132" s="21"/>
+    </row>
+    <row r="133" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="E133"/>
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="J133" s="21"/>
+    </row>
+    <row r="134" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
+      <c r="G134"/>
+      <c r="J134" s="21"/>
+    </row>
+    <row r="135" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+      <c r="D135"/>
+      <c r="E135"/>
+      <c r="F135"/>
+      <c r="G135"/>
+      <c r="J135" s="21"/>
+    </row>
+    <row r="136" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+      <c r="D136"/>
+      <c r="E136"/>
+      <c r="F136"/>
+      <c r="G136"/>
+      <c r="J136" s="21"/>
+    </row>
+    <row r="137" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A137"/>
+      <c r="B137"/>
+      <c r="C137"/>
+      <c r="D137"/>
+      <c r="E137"/>
+      <c r="F137"/>
+      <c r="G137"/>
+      <c r="J137" s="21"/>
+    </row>
+    <row r="138" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="J138" s="21"/>
+    </row>
+    <row r="139" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="J139" s="21"/>
+    </row>
+    <row r="140" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A140"/>
+      <c r="B140"/>
+      <c r="C140"/>
+      <c r="D140"/>
+      <c r="E140"/>
+      <c r="F140"/>
+      <c r="G140"/>
+    </row>
+    <row r="141" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+      <c r="D141"/>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141"/>
+      <c r="J141" s="21"/>
+    </row>
+    <row r="142" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142"/>
+      <c r="J142" s="21"/>
+    </row>
+    <row r="143" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+      <c r="D143"/>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143"/>
+      <c r="J143" s="21"/>
+    </row>
+    <row r="144" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="J144" s="21"/>
+    </row>
+    <row r="145" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="J145" s="21"/>
+    </row>
+    <row r="146" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="J146" s="21"/>
+    </row>
+    <row r="147" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147"/>
+      <c r="J147" s="21"/>
+    </row>
+    <row r="148" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+      <c r="D148"/>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148"/>
+      <c r="J148" s="21"/>
+    </row>
+    <row r="149" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+      <c r="D149"/>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149"/>
+      <c r="J149" s="21"/>
+    </row>
+    <row r="150" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+      <c r="D150"/>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150"/>
+      <c r="J150" s="21"/>
+    </row>
+    <row r="151" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A151"/>
+      <c r="B151"/>
+      <c r="C151"/>
+      <c r="D151"/>
+      <c r="E151"/>
+      <c r="F151"/>
+      <c r="G151"/>
+      <c r="J151" s="21"/>
+    </row>
+    <row r="152" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A152"/>
+      <c r="B152"/>
+      <c r="C152"/>
+      <c r="D152"/>
+      <c r="E152"/>
+      <c r="F152"/>
+      <c r="G152"/>
+      <c r="J152" s="21"/>
+    </row>
+    <row r="153" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A153"/>
+      <c r="B153"/>
+      <c r="C153"/>
+      <c r="D153"/>
+      <c r="E153"/>
+      <c r="F153"/>
+      <c r="G153"/>
+      <c r="J153" s="21"/>
+    </row>
+    <row r="173" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J173" s="20"/>
+    </row>
+    <row r="183" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J183" s="19"/>
+    </row>
+    <row r="216" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J216" s="20"/>
+    </row>
+    <row r="226" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J226" s="19"/>
+    </row>
+    <row r="259" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J259" s="20"/>
+    </row>
+    <row r="269" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J269" s="19"/>
+    </row>
+    <row r="302" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J302" s="20"/>
+    </row>
+    <row r="312" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J312" s="19"/>
+    </row>
+    <row r="345" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J345" s="20"/>
+    </row>
+    <row r="355" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J355" s="19"/>
+    </row>
+    <row r="388" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J388" s="20"/>
+    </row>
+    <row r="398" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J398" s="19"/>
+    </row>
+    <row r="431" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J431" s="20"/>
+    </row>
+    <row r="441" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J441" s="19"/>
+    </row>
+    <row r="474" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J474" s="20"/>
+    </row>
+    <row r="484" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J484" s="19"/>
+    </row>
+    <row r="517" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J517" s="20"/>
+    </row>
+    <row r="527" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J527" s="19"/>
+    </row>
+    <row r="560" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J560" s="20"/>
+    </row>
+    <row r="570" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J570" s="19"/>
+    </row>
+    <row r="603" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J603" s="20"/>
+    </row>
+    <row r="613" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J613" s="19"/>
+    </row>
+    <row r="646" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J646" s="20"/>
+    </row>
+    <row r="656" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J656" s="19"/>
+    </row>
+    <row r="689" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J689" s="20"/>
+    </row>
+    <row r="699" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J699" s="19"/>
+    </row>
+    <row r="732" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J732" s="20"/>
+    </row>
+    <row r="742" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J742" s="19"/>
+    </row>
+    <row r="775" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J775" s="20"/>
+    </row>
+    <row r="785" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J785" s="19"/>
+    </row>
+    <row r="818" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J818" s="20"/>
+    </row>
+    <row r="828" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J828" s="19"/>
+    </row>
+    <row r="861" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J861" s="20"/>
+    </row>
+    <row r="871" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J871" s="19"/>
+    </row>
+    <row r="904" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J904" s="20"/>
+    </row>
+    <row r="914" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J914" s="19"/>
+    </row>
+    <row r="947" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J947" s="20"/>
+    </row>
+    <row r="957" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J957" s="19"/>
+    </row>
+    <row r="990" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J990" s="20"/>
+    </row>
+    <row r="1000" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J1000" s="19"/>
+    </row>
+    <row r="1033" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J1033" s="20"/>
+    </row>
+    <row r="1043" spans="10:10" x14ac:dyDescent="0.3">
+      <c r="J1043" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
